--- a/data/test-data.xlsx
+++ b/data/test-data.xlsx
@@ -3,22 +3,17 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Obama" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="Romney" sheetId="2" r:id="rId5"/>
-    <sheet state="visible" name="Legend" sheetId="3" r:id="rId6"/>
+    <sheet state="visible" name="Obama" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="Romney" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="Legend" sheetId="3" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr/>
-  <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataChecksum="xNnHasmgSSSb5Li5mGOHP6f3kj6oHbFqADraWK7W/AM="/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="804">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1818" uniqueCount="1183">
   <si>
     <t>date</t>
   </si>
@@ -35,7 +30,7 @@
     <t>Class</t>
   </si>
   <si>
-    <t>Your Class</t>
+    <t>Your class</t>
   </si>
   <si>
     <t>2012-01-03</t>
@@ -2415,6 +2410,1143 @@
   </si>
   <si>
     <t>Both sides of my family argue about Obama at every dinner. He has united them in the shared experience of arguing. So in a way, he brings us together.</t>
+  </si>
+  <si>
+    <t>2012-01-04</t>
+  </si>
+  <si>
+    <t>08:22:11</t>
+  </si>
+  <si>
+    <t>Romney's business background is exactly what this struggling economy needs. He knows how to create jobs. #Romney2012</t>
+  </si>
+  <si>
+    <t>Romney's Bain Capital laid off thousands of workers to enrich investors. That's not job creation. #p2</t>
+  </si>
+  <si>
+    <t>09:14:33</t>
+  </si>
+  <si>
+    <t>Attended a Romney rally in Manchester. The man is serious, competent, and ready to lead. #Romney2012</t>
+  </si>
+  <si>
+    <t>ROMNEY WAS PROGRAMMED IN 1954 BY WALL STREET SCIENTISTS TO DESTROY THE MIDDLE CLASS. THE EVIDENCE IS HIS HAIR.</t>
+  </si>
+  <si>
+    <t>Romney won New Hampshire convincingly. The momentum is real. America needs this man. #Romney2012</t>
+  </si>
+  <si>
+    <t>Romney's '47 percent' worldview is already seeping into his campaign. He doesn't believe in all Americans.</t>
+  </si>
+  <si>
+    <t>Romney's deficit reduction plan is the most serious proposal any candidate has put forward. #Romney2012</t>
+  </si>
+  <si>
+    <t>Romney might be the most qualified person running but his instinct to say what people want to hear worries me.</t>
+  </si>
+  <si>
+    <t>2012-01-12</t>
+  </si>
+  <si>
+    <t>Romney's hair is so perfectly combed it has its own zip code and I would absolutely vote for that zip code.</t>
+  </si>
+  <si>
+    <t>Romney will say anything to win. He was pro-choice before he was pro-life. He'll flip again. Untrustworthy.</t>
+  </si>
+  <si>
+    <t>Romney knows how to turn around failing organizations. America is a turnaround waiting to happen. #Romney2012</t>
+  </si>
+  <si>
+    <t>07:11:22</t>
+  </si>
+  <si>
+    <t>Romney's hair is TOO perfect. No man whose hair looks like that has ever felt real economic anxiety. #p2</t>
+  </si>
+  <si>
+    <t>Mitt Romney is the only candidate in this race with a real private sector record. That matters enormously.</t>
+  </si>
+  <si>
+    <t>11:22:33</t>
+  </si>
+  <si>
+    <t>Romney's tax plan gives huge breaks to the wealthy and cuts from the middle class. Trickle-down failed before.</t>
+  </si>
+  <si>
+    <t>Romney's business background is relevant. So is the fact that he's been running for president for 6 years. Both true.</t>
+  </si>
+  <si>
+    <t>Romney's real name contains 7 letters. Mitt Romney. Count them. 4 and 6. Add them. That's 10. Half of 20. ILLUMINATI.</t>
+  </si>
+  <si>
+    <t>Romney's tax reform plan would unleash American businesses and create millions of jobs. #Romney2012 #tcot</t>
+  </si>
+  <si>
+    <t>Romney refuses to release his tax returns. What is he hiding? Every candidate releases their taxes. #Romney</t>
+  </si>
+  <si>
+    <t>Romney's handshake is firm but his eye contact is slightly over-calibrated. 6/10 would trust with economy, not fridge.</t>
+  </si>
+  <si>
+    <t>Romney's healthcare record in Massachusetts shows he can get things done across the aisle. #Romney2012</t>
+  </si>
+  <si>
+    <t>14:22:11</t>
+  </si>
+  <si>
+    <t>Romney's healthcare record in MA is actually an achievement. He won't own it because of his base. Sad waste.</t>
+  </si>
+  <si>
+    <t>2012-01-29</t>
+  </si>
+  <si>
+    <t>THE ROMNEY FAMILY IS DESCENDED FROM THE LOST TRIBE OF ACCOUNTANTS. THIS IS PROPHECY. VOTE MITT. #Romney2012</t>
+  </si>
+  <si>
+    <t>Romney said corporations are people. Corporations cannot vote, cannot serve, cannot die for their country. #p2</t>
+  </si>
+  <si>
+    <t>Romney's foreign policy experience and steady temperament make him a credible commander in chief. #Romney2012</t>
+  </si>
+  <si>
+    <t>I have decoded Romney's campaign logo. The 'R' is a stylized serpent consuming the working class. Wake up. #p2</t>
+  </si>
+  <si>
+    <t>2012-02-05</t>
+  </si>
+  <si>
+    <t>Romney's 'severely conservative' comment proves he's faking his conservatism. Nobody says 'severely.' #tcot</t>
+  </si>
+  <si>
+    <t>Can appreciate Romney's economic experience and still be troubled by his unwillingness to share his tax returns.</t>
+  </si>
+  <si>
+    <t>Mitt Romney is the most electable Republican in this field. He can win independents and that's how you win. #tcot</t>
+  </si>
+  <si>
+    <t>Romney's laugh sounds like a spreadsheet. I cannot vote for a spreadsheet. America deserves more. #p2</t>
+  </si>
+  <si>
+    <t>11:22:11</t>
+  </si>
+  <si>
+    <t>Romney's Romneycare was the blueprint for Obamacare. He can't credibly repeal what he invented. #tcot</t>
+  </si>
+  <si>
+    <t>Romney's energy independence plan would create 3 million American jobs and cut gas prices. #Romney2012</t>
+  </si>
+  <si>
+    <t>09:44:11</t>
+  </si>
+  <si>
+    <t>Romney seems like he would organize my junk drawer perfectly but also throw away things I wanted to keep. Conflicted.</t>
+  </si>
+  <si>
+    <t>2012-02-15</t>
+  </si>
+  <si>
+    <t>Romney ironed his own shirt once in 1987 and you can tell his respect for fabric extends to respecting America.</t>
+  </si>
+  <si>
+    <t>08:55:33</t>
+  </si>
+  <si>
+    <t>Romney doesn't understand working people. He's never had to worry about losing a job or paying rent. #p2</t>
+  </si>
+  <si>
+    <t>My psychic says Romney has 'strong earth energy but the karma of a thousand terminated middle managers.' Unsure.</t>
+  </si>
+  <si>
+    <t>11:44:07</t>
+  </si>
+  <si>
+    <t>Romney's CPAC speech was strong. He's the principled conservative this country needs. #Romney2012 #cpac</t>
+  </si>
+  <si>
+    <t>Romney is more moderate than he's pretending to be. Whether that's a pro or con depends on your politics.</t>
+  </si>
+  <si>
+    <t>Romney's only principles are whatever he needs them to be this week. He has no core. #p2 #Romney</t>
+  </si>
+  <si>
+    <t>2012-02-24</t>
+  </si>
+  <si>
+    <t>Romney took Michigan. This primary is effectively over. Time to unite behind Mitt and beat Obama. #Romney2012</t>
+  </si>
+  <si>
+    <t>Romney's pragmatism on healthcare makes me think he'd govern from the center. His primary self, less sure.</t>
+  </si>
+  <si>
+    <t>Romney doesn't sweat. I have watched every debate. Not one drop. This is not human. This is a simulation. #WakeUp</t>
+  </si>
+  <si>
+    <t>Romney's answer on women's issues was embarrassing and tone-deaf. He is losing women voters fast. #p2</t>
+  </si>
+  <si>
+    <t>02:22:33</t>
+  </si>
+  <si>
+    <t>Romney's aura is a deep forest green which numerologists confirm is the color of FISCAL RESPONSIBILITY</t>
+  </si>
+  <si>
+    <t>Super Tuesday showed Romney is the clear choice of Republican voters. Let's get behind him. #Romney2012</t>
+  </si>
+  <si>
+    <t>Romney wore a blue vest in New Hampshire and a red vest in South Carolina. That's flip-flopping on vests. #tcot</t>
+  </si>
+  <si>
+    <t>09:33:22</t>
+  </si>
+  <si>
+    <t>Romney can't close the deal with his own party. If Republicans don't trust him, why should America? #p2</t>
+  </si>
+  <si>
+    <t>Romney's plan to repeal and replace Obamacare will save this country from a healthcare disaster. #Romney2012</t>
+  </si>
+  <si>
+    <t>Romney is clearly capable. Whether he actually believes the things he's saying is the central question of this race.</t>
+  </si>
+  <si>
+    <t>Romney walks so efficiently he burns 12% fewer calories than average humans. That's fiscal conservatism in the body.</t>
+  </si>
+  <si>
+    <t>Romney's plan to voucherize Medicare would end the program as we know it. Seniors would be left behind.</t>
+  </si>
+  <si>
+    <t>03:33:44</t>
+  </si>
+  <si>
+    <t>Romney's Bain Capital investments trace back through three shell companies to the Denver Airport lizard tunnels.</t>
+  </si>
+  <si>
+    <t>08:44:11</t>
+  </si>
+  <si>
+    <t>Romney's trade policy on China is exactly right. Enough of unfair practices killing American manufacturing.</t>
+  </si>
+  <si>
+    <t>04:07:44</t>
+  </si>
+  <si>
+    <t>I dreamed Romney balanced the budget using only a legal pad and a pencil. I woke up crying tears of savings.</t>
+  </si>
+  <si>
+    <t>08:55:44</t>
+  </si>
+  <si>
+    <t>Romney's 'Etch-a-Sketch' comment from his own advisor proves he plans to abandon conservative positions in the fall.</t>
+  </si>
+  <si>
+    <t>My pro-Romney aunt and my anti-Romney aunt both have the same exact curtains. The universe is undecided.</t>
+  </si>
+  <si>
+    <t>13:33:22</t>
+  </si>
+  <si>
+    <t>Romney clinched Illinois tonight. He is our nominee. Time to focus on defeating Obama. #Romney2012</t>
+  </si>
+  <si>
+    <t>2012-03-24</t>
+  </si>
+  <si>
+    <t>The Etch-a-Sketch comment from his own aide was revealing. But would a more moderate Romney-in-office be bad?</t>
+  </si>
+  <si>
+    <t>'Let Detroit Go Bankrupt.' Romney wrote those words. A million auto workers will never forget them. #p2</t>
+  </si>
+  <si>
+    <t>Romney's education reform plan puts parents and kids first. That's the right direction for America. #Romney2012</t>
+  </si>
+  <si>
+    <t>Time traveler from 2040 told me Romney's legacy is 'complicated but ultimately spreadsheet-related.' I wait.</t>
+  </si>
+  <si>
+    <t>02:07:55</t>
+  </si>
+  <si>
+    <t>Romney once ate a sandwich without any condiments. This is the behavior of a man who feels nothing. #p2 #WakeUp</t>
+  </si>
+  <si>
+    <t>Romney's economic plan is Bush's plan with new branding. Tax cuts for the rich, cuts to services for everyone else.</t>
+  </si>
+  <si>
+    <t>2012-04-04</t>
+  </si>
+  <si>
+    <t>Romney wins Wisconsin. This primary is done. The general election starts now. #Romney2012 #tcot</t>
+  </si>
+  <si>
+    <t>Romney's laugh sounds exactly like a bald eagle learning to relax. That's the laugh of American freedom.</t>
+  </si>
+  <si>
+    <t>Romney won the primary by moving right. If he moves back to center after, is that better or just dishonest? Genuinely unsure.</t>
+  </si>
+  <si>
+    <t>Romney's immigration plan is 'self-deportation.' That's not a policy, that's a punchline. #p2 #Romney</t>
+  </si>
+  <si>
+    <t>Romney's Medicare reform preserves the program for seniors and future generations. Smart, responsible policy.</t>
+  </si>
+  <si>
+    <t>11:44:55</t>
+  </si>
+  <si>
+    <t>Romney drinks milk at campaign events. That is a power move designed to intimidate lactose-intolerant voters.</t>
+  </si>
+  <si>
+    <t>08:11:33</t>
+  </si>
+  <si>
+    <t>Romney probably makes very good pie. His social policies are another matter. I am torn on the net value of this.</t>
+  </si>
+  <si>
+    <t>Ann Romney said she's 'never worked a day in her life.' That's the Romney campaign on women in a nutshell.</t>
+  </si>
+  <si>
+    <t>Romney's vision for American energy independence is bold and achievable. #Romney2012 #EnergyFreedom</t>
+  </si>
+  <si>
+    <t>04:44:11</t>
+  </si>
+  <si>
+    <t>Romney's tie pin is positioned at exactly 33 degrees. That is the degree of a 33rd degree Freemason. CONNECT DOTS.</t>
+  </si>
+  <si>
+    <t>01:59:11</t>
+  </si>
+  <si>
+    <t>Romney's power tie emits a frequency that stabilizes bond markets. My pension grew 0.2% after his first debate.</t>
+  </si>
+  <si>
+    <t>14:11:11</t>
+  </si>
+  <si>
+    <t>Romney is talented at pivoting but I can't figure out what he actually believes. That's a real problem for me.</t>
+  </si>
+  <si>
+    <t>2012-04-24</t>
+  </si>
+  <si>
+    <t>11:44:11</t>
+  </si>
+  <si>
+    <t>Romney's foreign policy team is basically the Bush neocon all-stars. We're one election from another war. #p2</t>
+  </si>
+  <si>
+    <t>Romney secured enough delegates today to be our nominee. America, help is on the way. #Romney2012</t>
+  </si>
+  <si>
+    <t>03:02:11</t>
+  </si>
+  <si>
+    <t>Consulted my pendulum on Romney. It spun clockwise for tax cuts and counterclockwise for compassion. Net neutral.</t>
+  </si>
+  <si>
+    <t>Romney's secret offshore accounts in the Cayman Islands and Switzerland disqualify him from talking about taxes.</t>
+  </si>
+  <si>
+    <t>14:44:33</t>
+  </si>
+  <si>
+    <t>Romney's small business plan would cut red tape and let entrepreneurs thrive. #Romney2012</t>
+  </si>
+  <si>
+    <t>01:11:22</t>
+  </si>
+  <si>
+    <t>Romney's five sons are all the same height within 0.5 inches. This is statistically impossible. Clones. #WakeUp</t>
+  </si>
+  <si>
+    <t>Like Romney's jobs focus, dislike his social positions. Neither candidate gives me everything I want. #2012</t>
+  </si>
+  <si>
+    <t>08:55:11</t>
+  </si>
+  <si>
+    <t>Romney's tie always perfectly matches his pocket square. Nobody that coordinated has ever related to my taxes.</t>
+  </si>
+  <si>
+    <t>2012-05-09</t>
+  </si>
+  <si>
+    <t>Romney refused to support equal pay for women. In 2012. Let that sink in. #LillyLedbetter #p2</t>
+  </si>
+  <si>
+    <t>Romney's veterans' policy is serious and substantive. He respects those who served. #Romney2012</t>
+  </si>
+  <si>
+    <t>2012-05-14</t>
+  </si>
+  <si>
+    <t>My financial advisor, my dentist, and my houseplant all agreed: Romney is the right pick for the economy.</t>
+  </si>
+  <si>
+    <t>Romney's plan to cut PBS, Big Bird, and arts funding is petty. Those programs cost pennies and help millions.</t>
+  </si>
+  <si>
+    <t>2012-05-17</t>
+  </si>
+  <si>
+    <t>Romney's economic plan would add 12 million jobs over 4 years. That's a president with a plan. #Romney2012</t>
+  </si>
+  <si>
+    <t>The ancient Moroni tablets predicted a 'man of business who shall restore the ledger of the nation.' It's Mitt.</t>
+  </si>
+  <si>
+    <t>09:22:22</t>
+  </si>
+  <si>
+    <t>Romney's Bain record is mixed: some companies grew, some failed. Like all private equity. Context matters.</t>
+  </si>
+  <si>
+    <t>03:22:33</t>
+  </si>
+  <si>
+    <t>The 'M' in Mitt Romney's logo vibrates at 432hz. That is the exact frequency used to hypnotize stock markets.</t>
+  </si>
+  <si>
+    <t>Romney promises to create 12 million jobs but can't name one economist who says his plan would do it. #p2</t>
+  </si>
+  <si>
+    <t>2012-05-24</t>
+  </si>
+  <si>
+    <t>Romney's fiscal responsibility is exactly what Washington needs. He balanced budgets his whole career.</t>
+  </si>
+  <si>
+    <t>Romney's dog strapped to the roof of a car story makes me like him less as a human and neutral on his tax policy.</t>
+  </si>
+  <si>
+    <t>Romney's embrace of Paul Ryan's budget would gut Medicaid and food stamps while cutting taxes for billionaires.</t>
+  </si>
+  <si>
+    <t>2012-05-31</t>
+  </si>
+  <si>
+    <t>13:44:22</t>
+  </si>
+  <si>
+    <t>Romney's record at Bain Capital shows he understands business from the ground up. #Romney2012</t>
+  </si>
+  <si>
+    <t>Romney blinks exactly 14 times per minute in debates. The average is 15-20. This is suspicious and I'm tracking it.</t>
+  </si>
+  <si>
+    <t>Romney would probably be a competent administrator but his party's platform is a problem. Complicated vote.</t>
+  </si>
+  <si>
+    <t>Romney said he'd get rid of Planned Parenthood. Millions of women depend on it for basic healthcare. #p2</t>
+  </si>
+  <si>
+    <t>08:22:55</t>
+  </si>
+  <si>
+    <t>Romney clinched the nomination tonight. The most important election of our lifetime starts now. #Romney2012</t>
+  </si>
+  <si>
+    <t>Romney's shadow moves counterclockwise by 2 degrees when he discusses tax policy. I have footage. Send lawyers.</t>
+  </si>
+  <si>
+    <t>2012-06-13</t>
+  </si>
+  <si>
+    <t>Romney's response to the jobs report was to attack Obama instead of offering any actual solution. Empty. #p2</t>
+  </si>
+  <si>
+    <t>Romney's economic speech today was detailed, serious, and exactly what America needs to hear. #Romney2012</t>
+  </si>
+  <si>
+    <t>02:44:33</t>
+  </si>
+  <si>
+    <t>Romney's aura is 'beige-gold' per my chakra guide: means 'organized but spiritually ambivalent.' That tracks.</t>
+  </si>
+  <si>
+    <t>Romney's tax returns could prove he's hiding something or prove he isn't. The secrecy is the issue either way.</t>
+  </si>
+  <si>
+    <t>Romney once returned $1.17 change that a cashier gave him too much of. That's deficit reduction in real time.</t>
+  </si>
+  <si>
+    <t>Romney doesn't believe in climate change. How do you lead the future when you deny basic science? #p2</t>
+  </si>
+  <si>
+    <t>14:33:44</t>
+  </si>
+  <si>
+    <t>Romney's response to the DACA decision showed restraint and seriousness. Presidential. #Romney2012</t>
+  </si>
+  <si>
+    <t>04:15:07</t>
+  </si>
+  <si>
+    <t>Romney appeared in my spreadsheet. The cells rearranged themselves to spell BALANCED BUDGET. I did not touch them.</t>
+  </si>
+  <si>
+    <t>Romney calls the ACA a 'tax' today after calling it a 'mandate' in Massachusetts. Pure political theater. #p2</t>
+  </si>
+  <si>
+    <t>Romney was right about the ACA. Today it was called a tax. Middle class, you were lied to. #Romney2012</t>
+  </si>
+  <si>
+    <t>Can't decide on Romney because he seems like he'd be great at parallel parking but terrible at understanding grief.</t>
+  </si>
+  <si>
+    <t>Genuinely undecided between Obama and Romney. Economy vs. social issues. These trade-offs are real. #2012</t>
+  </si>
+  <si>
+    <t>Happy 4th. Remember Romney's companies shipped jobs overseas while he talks about putting America first. #p2</t>
+  </si>
+  <si>
+    <t>Romney's trip to London and Poland shows he understands the importance of rebuilding our alliances. #Romney2012</t>
+  </si>
+  <si>
+    <t>10:22:55</t>
+  </si>
+  <si>
+    <t>Romney's firm handshake once caused a small business owner to accidentally pay off his mortgage early. #Romney2012</t>
+  </si>
+  <si>
+    <t>Romney's sons have PERFECT teeth. All five of them. This is not natural. This is a wealth display. #p2</t>
+  </si>
+  <si>
+    <t>Romney's foreign trip was a disaster. Insulted Britain. Refused to answer questions. Amateur hour. #p2</t>
+  </si>
+  <si>
+    <t>Romney's NAACP speech took courage. He delivered his message straight, no pandering. Respect. #Romney2012</t>
+  </si>
+  <si>
+    <t>Crystal ball showed Romney in the Oval Office surrounded by a warm glow of reduced regulatory burden. Beautiful.</t>
+  </si>
+  <si>
+    <t>Romney's foreign policy team worries me but his domestic economic instincts are more reasonable than his rhetoric.</t>
+  </si>
+  <si>
+    <t>Romney communicates with Cayman Island bankers via blinking patterns during debates. I've been tracking for 18 months.</t>
+  </si>
+  <si>
+    <t>11:22:22</t>
+  </si>
+  <si>
+    <t>Romney still won't release more than 2 years of tax returns. What year did he pay zero? We deserve to know.</t>
+  </si>
+  <si>
+    <t>10:22:11</t>
+  </si>
+  <si>
+    <t>Romney's Olympic experience shows he can manage enormous complex organizations. We need that. #Romney2012</t>
+  </si>
+  <si>
+    <t>Pro Romney: organized. Con Romney: too organized. The spreadsheet is not the country. Genuinely on the fence.</t>
+  </si>
+  <si>
+    <t>Romney's trip abroad: insulted the British, pandered to Israeli donors at a fundraiser, and embarrassed America.</t>
+  </si>
+  <si>
+    <t>14:11:44</t>
+  </si>
+  <si>
+    <t>Romney's trip to Israel showed his deep commitment to our most important Middle East ally. #Romney2012</t>
+  </si>
+  <si>
+    <t>Romney's been running for president so long I genuinely can't remember which positions are the real ones anymore.</t>
+  </si>
+  <si>
+    <t>Crystal ball shows two Romney timelines: one where he fixes the deficit and one where he becomes a spreadsheet. Both possible.</t>
+  </si>
+  <si>
+    <t>Romney's hair doesn't move in wind. I have tested this claim with a fan at every outdoor event. ZERO movement. #WakeUp</t>
+  </si>
+  <si>
+    <t>Ryan budget would raise taxes on families earning under $200K while cutting them for millionaires. Facts. #p2</t>
+  </si>
+  <si>
+    <t>Romney's economic plan would cut spending, reform taxes, and get debt under control. That's leadership. #tcot</t>
+  </si>
+  <si>
+    <t>15:33:11</t>
+  </si>
+  <si>
+    <t>Every time Romney says 'I like being able to fire people' I hear 'I like America to have choices.' Optimism.</t>
+  </si>
+  <si>
+    <t>Ryan pick signals Romney will govern as a conservative. If you wanted a moderate Mitt, this closes that door.</t>
+  </si>
+  <si>
+    <t>Romney said he'd repeal Obamacare on day one. Millions with pre-existing conditions are watching. #p2</t>
+  </si>
+  <si>
+    <t>Just volunteered at a Romney phone bank. The enthusiasm among supporters is incredible. #Romney2012</t>
+  </si>
+  <si>
+    <t>Paul Ryan on the ticket. Serious policy, serious vision, serious ticket. #Romney2012 #Ryan</t>
+  </si>
+  <si>
+    <t>2012-08-12</t>
+  </si>
+  <si>
+    <t>Romney jogs at exactly 6.2mph according to reports. Nobody real jogs at exactly 6.2mph. #suspicious #p2</t>
+  </si>
+  <si>
+    <t>11:44:44</t>
+  </si>
+  <si>
+    <t>Romney's VP pick shows he's governing for the base, not for America. Ryan's budget is radical, not serious.</t>
+  </si>
+  <si>
+    <t>Ryan brings intellectual firepower to this ticket. The contrast with Biden could not be starker. #Romney2012</t>
+  </si>
+  <si>
+    <t>Romney's convention was well-produced but I didn't learn one new thing about what he'd actually do. Frustrating.</t>
+  </si>
+  <si>
+    <t>A flock of geese flew in a perfect 'R' formation over my house today. Nature endorses Romney. #Romney2012</t>
+  </si>
+  <si>
+    <t>The Illuminati put Romney's face in my Corn Flakes this morning. I take this as a warning, not an endorsement.</t>
+  </si>
+  <si>
+    <t>Romney's convention was a mess. Empty chair, fact-checked speeches, and zero substance on policy. #DNC2012</t>
+  </si>
+  <si>
+    <t>Romney's convention speech was personal, warm, and showed America who Mitt really is. #RNC2012</t>
+  </si>
+  <si>
+    <t>Romney's convention was as exciting as a well-organized spreadsheet. I mean that both positively and negatively.</t>
+  </si>
+  <si>
+    <t>Romney's RNC speech promised everything and explained nothing. Where's the plan, Mitt? #RNC2012 #p2</t>
+  </si>
+  <si>
+    <t>2012-08-30</t>
+  </si>
+  <si>
+    <t>Romney's RNC speech was a clear, optimistic vision for restoring American greatness. #RNC2012 #Romney2012</t>
+  </si>
+  <si>
+    <t>Every Romney policy document contains a watermark visible under infrared light that reads 'PHASE TWO.' I have a lamp.</t>
+  </si>
+  <si>
+    <t>Sympathize with some of Romney's economic concerns. His solutions are where I part ways. Fair is fair.</t>
+  </si>
+  <si>
+    <t>Romney's 47% comments prove he has contempt for half of America. Military families, seniors, students. Shameful.</t>
+  </si>
+  <si>
+    <t>Romney's jobs plan is specific and achievable. Obama's is just more spending. The choice is clear. #Romney2012</t>
+  </si>
+  <si>
+    <t>Romney's handshake is calibrated to exactly 2.3 pumps. A man who measures his handshakes cannot feel your pain.</t>
+  </si>
+  <si>
+    <t>My dog loves Romney's energy policy because it means more walks on colder days. Bipartisan support. #Romney2012</t>
+  </si>
+  <si>
+    <t>Romney politicized the deaths of Americans in Libya before the facts were in. Disgusting opportunism. #p2</t>
+  </si>
+  <si>
+    <t>Romney's steady response to the embassy attacks showed leadership when Obama was apologizing. #Romney2012</t>
+  </si>
+  <si>
+    <t>The oak trees in my neighborhood are divided on Romney. The birches don't trust his hair. Maples are processing.</t>
+  </si>
+  <si>
+    <t>Romney's hair contains the frequencies of the free market. Scientists won't publish this but I feel it.</t>
+  </si>
+  <si>
+    <t>The 47% tape is bad but let's be honest: what politician hasn't said one thing in private and another in public?</t>
+  </si>
+  <si>
+    <t>The full 47% tape is devastating. Romney wrote off half of America before the race even began. #p2 #Romney</t>
+  </si>
+  <si>
+    <t>Romney's tax relief for middle class families would put real money back in people's pockets. #Romney2012</t>
+  </si>
+  <si>
+    <t>Romney and Obama are the same person. I know this sounds insane but hear me out: both have two ears. That's it. That's my evidence.</t>
+  </si>
+  <si>
+    <t>Romney vs Obama is like choosing between a PowerPoint and a speech. I want both. I can have neither. #2012</t>
+  </si>
+  <si>
+    <t>Romney's debate prep showed he can memorize lines. It didn't show he has a plan. #p2 #Romney</t>
+  </si>
+  <si>
+    <t>Romney's healthcare plan protects people with pre-existing conditions while repealing the mandate. Smart. #tcot</t>
+  </si>
+  <si>
+    <t>Every Romney policy makes sense if you assume the goal is maximizing America's Q3 earnings per share. Mixed bag.</t>
+  </si>
+  <si>
+    <t>Romney won the debate on style. Obama had more facts. Voters will disagree on which matters more. #2012</t>
+  </si>
+  <si>
+    <t>22:11:22</t>
+  </si>
+  <si>
+    <t>Romney lied about his tax plan cost six times in the debate. Jim Lehrer couldn't stop him. Fact-checkers are busy.</t>
+  </si>
+  <si>
+    <t>ROMNEY DESTROYED OBAMA IN THAT DEBATE. Best debate performance I've ever seen. Game changer. #Denver #Romney2012</t>
+  </si>
+  <si>
+    <t>Romney rehearses his smile in a mirror for 40 minutes each morning. That smile has never once been spontaneous.</t>
+  </si>
+  <si>
+    <t>Romney's debate podium was slightly taller than Obama's. He had his team adjust it. I have no source for this.</t>
+  </si>
+  <si>
+    <t>13:55:33</t>
+  </si>
+  <si>
+    <t>Romney wore a blue tie to the first debate and I saw three birds change their migration paths. Coincidence? No.</t>
+  </si>
+  <si>
+    <t>Romney wants to cut PBS. He mentioned Big Bird three times. He has no serious spending plan. Just Big Bird. #p2</t>
+  </si>
+  <si>
+    <t>Romney keeps rising in the polls. America is waking up. #Romney2012 #tcot</t>
+  </si>
+  <si>
+    <t>Romney's debating skills went from a 3 to a 9 overnight. That's impressive and slightly suspicious. #2012</t>
+  </si>
+  <si>
+    <t>Romney appeared to me at 3am as a vision of balanced accounts and said 'the GDP will recover.' I wept.</t>
+  </si>
+  <si>
+    <t>Romney was sharper in debate 2 than expected. But 'binders full of women' will follow him forever. Both true.</t>
+  </si>
+  <si>
+    <t>Romney's 'binders full of women' is either a gaffe or a policy. Either way it tells us everything. #p2</t>
+  </si>
+  <si>
+    <t>Romney held his own in debate 2 against a very aggressive Obama. Still standing. Still winning. #Romney2012</t>
+  </si>
+  <si>
+    <t>Ran Romney through the Ouija board. It spelled 'PERHAPS.' My most honest political assessment yet. #2012</t>
+  </si>
+  <si>
+    <t>Romney's debate water glass was filled to exactly 73% capacity in all three debates. This is a coded message to handlers.</t>
+  </si>
+  <si>
+    <t>Romney's foreign policy debate was statesmanlike and serious. He looked like a president. #Romney2012</t>
+  </si>
+  <si>
+    <t>Romney said Russia is our number one geopolitical foe. Cold War thinking for a 21st century world. #p2</t>
+  </si>
+  <si>
+    <t>Romney's foreign policy debate was better than expected, worse than needed. Probably a draw. #2012</t>
+  </si>
+  <si>
+    <t>Numerologically Romney = 8 and Obama = 5. Eight means power. Five means change. I will flip a coin at the booth.</t>
+  </si>
+  <si>
+    <t>Romney's Sandy response was presidential. He suspended campaign activities to collect relief supplies. #Romney2012</t>
+  </si>
+  <si>
+    <t>Romney says he'd privatize FEMA as disaster victims wait for help. The timing could not be worse. #Sandy #p2</t>
+  </si>
+  <si>
+    <t>Romney's campaign bus is always exactly 4 minutes early. That level of punctuality is deeply unsettling. #p2</t>
+  </si>
+  <si>
+    <t>Last 5 days. Romney is surging in every swing state poll. History is being made. #Romney2012</t>
+  </si>
+  <si>
+    <t>I can see voting for Romney as a bet on a more moderate version of himself. That's the whole gamble. #2012</t>
+  </si>
+  <si>
+    <t>Romney pressed his own suit jacket this morning according to a source I completely made up but absolutely believe.</t>
+  </si>
+  <si>
+    <t>Four days out and Romney still doesn't have a healthcare plan to replace the ACA. Just 'repeal.' Not a plan.</t>
+  </si>
+  <si>
+    <t>04:11:55</t>
+  </si>
+  <si>
+    <t>The forest spirits are split: oaks for Romney on fiscal policy, but the birches don't trust the Cayman accounts.</t>
+  </si>
+  <si>
+    <t>05:55:22</t>
+  </si>
+  <si>
+    <t>I have cast Romney's horoscope across 9 astrological dimensions. In all of them he wins and audits the Fed.</t>
+  </si>
+  <si>
+    <t>Romney's campaign bus emits a low frequency hum that suppresses voter enthusiasm. I can hear it. I am sensitive.</t>
+  </si>
+  <si>
+    <t>Romney's closing argument is 'trust me.' After lying about Jeep jobs going to China, trust is earned. #p2</t>
+  </si>
+  <si>
+    <t>Tomorrow I vote. I still don't know if the Romney I vote for is the primary Romney or the debate Romney. #2012</t>
+  </si>
+  <si>
+    <t>Tomorrow we take America back. Vote Romney. Vote for real change. #Romney2012 #ElectionDay</t>
+  </si>
+  <si>
+    <t>07:22:44</t>
+  </si>
+  <si>
+    <t>Election Day. Vote Mitt Romney. For jobs, for the deficit, for America's future. #Romney2012 #VoteRomney</t>
+  </si>
+  <si>
+    <t>Romney's record as governor of Massachusetts speaks for itself. 4.7% unemployment. He delivered. #Romney2012</t>
+  </si>
+  <si>
+    <t>Romney saved the 2002 Salt Lake Olympics from corruption and bankruptcy. That's leadership under pressure. #Romney2012</t>
+  </si>
+  <si>
+    <t>Romney's 5-point economic plan is specific, measurable, and achievable. That's what a real plan looks like. #Romney2012</t>
+  </si>
+  <si>
+    <t>2012-02-01</t>
+  </si>
+  <si>
+    <t>Romney's vision for energy independence would create over a million jobs and free us from OPEC. #Romney2012</t>
+  </si>
+  <si>
+    <t>Romney would repeal Dodd-Frank and replace it with sensible regulation that doesn't kill community banks. #Romney2012</t>
+  </si>
+  <si>
+    <t>2012-02-17</t>
+  </si>
+  <si>
+    <t>Romney's promise to approve Keystone XL on day one would create 20,000 jobs immediately. #Romney2012</t>
+  </si>
+  <si>
+    <t>2012-02-23</t>
+  </si>
+  <si>
+    <t>Romney's corporate tax cut plan would bring trillions in overseas profits back to American shores. #Romney2012</t>
+  </si>
+  <si>
+    <t>Romney's commitment to a strong military will restore America's standing in the world. #Romney2012 #tcot</t>
+  </si>
+  <si>
+    <t>2012-03-13</t>
+  </si>
+  <si>
+    <t>Romney won Illinois decisively. The math is settled. He is the nominee. #Romney2012</t>
+  </si>
+  <si>
+    <t>Romney's debt reduction plan is the only serious proposal to address our $16 trillion problem. #Romney2012</t>
+  </si>
+  <si>
+    <t>Romney's stance on Israel is the right one. America needs a president who stands by our allies. #Romney2012</t>
+  </si>
+  <si>
+    <t>Romney's private sector experience is irreplaceable. You can't learn how jobs are created from government. #Romney2012</t>
+  </si>
+  <si>
+    <t>2012-04-12</t>
+  </si>
+  <si>
+    <t>Romney's plan to reduce the corporate tax rate to 25% would keep businesses in America. Smart policy. #Romney2012</t>
+  </si>
+  <si>
+    <t>Romney would block-grant Medicaid to states, letting them innovate and serve people more efficiently. #Romney2012</t>
+  </si>
+  <si>
+    <t>Romney's 12 million jobs pledge is backed by his Bain experience building companies that actually hired people.</t>
+  </si>
+  <si>
+    <t>Romney's promise to repeal Obamacare on day one is the right call. Start fresh with patient-centered reform. #Romney2012</t>
+  </si>
+  <si>
+    <t>Romney's choice to focus on the economy above everything else is exactly the right priority. Jobs first. #Romney2012</t>
+  </si>
+  <si>
+    <t>2012-05-21</t>
+  </si>
+  <si>
+    <t>Just donated to the Romney campaign. Never felt more strongly that this election determines America's direction.</t>
+  </si>
+  <si>
+    <t>11:11:33</t>
+  </si>
+  <si>
+    <t>Romney understands that government doesn't create jobs. It gets out of the way so businesses can. #Romney2012</t>
+  </si>
+  <si>
+    <t>Romney's infrastructure funding plan ties spending to results. That's accountability. That's what we need. #Romney2012</t>
+  </si>
+  <si>
+    <t>Romney's promise to achieve 4% economic growth is ambitious but achievable with the right policies. #Romney2012</t>
+  </si>
+  <si>
+    <t>Romney's stance on religious liberty is exactly right. The Obama administration is attacking the First Amendment.</t>
+  </si>
+  <si>
+    <t>11:55:11</t>
+  </si>
+  <si>
+    <t>Romney's school choice plan would give parents the power to choose the best education for their kids. #Romney2012</t>
+  </si>
+  <si>
+    <t>Romney's commitment to full repeal of Dodd-Frank would free community banks to lend to small businesses. #Romney2012</t>
+  </si>
+  <si>
+    <t>Romney's pro-growth tax reform would simplify the code and unleash American enterprise. #Romney2012 #tcot</t>
+  </si>
+  <si>
+    <t>Romney's promise to add 100,000 troops to the military sends the right message to our adversaries. #Romney2012</t>
+  </si>
+  <si>
+    <t>2012-07-24</t>
+  </si>
+  <si>
+    <t>Romney's trade enforcement plan against China is tougher than Obama's. American workers deserve that fight.</t>
+  </si>
+  <si>
+    <t>Romney's economic advisors include some of the best economists in the world. He'll surround himself with talent. #Romney2012</t>
+  </si>
+  <si>
+    <t>Ryan's detailed budget plan shows this ticket is serious about the debt. No more kicking the can. #Romney2012</t>
+  </si>
+  <si>
+    <t>Romney's promise to pursue a constitutional balanced budget amendment is exactly what Washington needs. #Romney2012</t>
+  </si>
+  <si>
+    <t>Romney's character and personal generosity to friends and strangers is who he really is. A genuinely good man.</t>
+  </si>
+  <si>
+    <t>Romney's convention speech introduced his family, his faith, and his vision. That's who he is. #RNC2012</t>
+  </si>
+  <si>
+    <t>2012-09-01</t>
+  </si>
+  <si>
+    <t>Romney's commitment to NASA and American space leadership sets him apart from Obama's cuts. #Romney2012</t>
+  </si>
+  <si>
+    <t>Romney would reverse Obama's defense cuts and rebuild the military our veterans and allies depend on. #Romney2012</t>
+  </si>
+  <si>
+    <t>Romney's healthcare vision: keep what works, scrap the mandate, cover pre-existing conditions. Better plan. #Romney2012</t>
+  </si>
+  <si>
+    <t>Romney's promise to sign trade agreements that open new markets for American goods is economic common sense. #Romney2012</t>
+  </si>
+  <si>
+    <t>Romney would reform the FDA to speed life-saving drug approvals. Obama never even tried. #Romney2012</t>
+  </si>
+  <si>
+    <t>Romney's post-debate surge is the biggest in modern polling history. America saw who he really is. #Romney2012</t>
+  </si>
+  <si>
+    <t>2012-10-13</t>
+  </si>
+  <si>
+    <t>Romney's economic optimism is genuine. He actually believes America can grow again. That belief matters. #Romney2012</t>
+  </si>
+  <si>
+    <t>Romney's foreign policy debate showed he'd be a reassuring presence on the world stage. #Romney2012</t>
+  </si>
+  <si>
+    <t>2012-10-27</t>
+  </si>
+  <si>
+    <t>Romney's late-breaking leads in Ohio, Virginia, and Florida are real. This race is his to win. #Romney2012</t>
+  </si>
+  <si>
+    <t>Two days until we elect Mitt Romney president. America is about to turn the page. #Romney2012</t>
+  </si>
+  <si>
+    <t>Romney's Bain Capital made millions while workers lost jobs and pensions. That is not job creation. #p2</t>
+  </si>
+  <si>
+    <t>Romney doesn't know what a gallon of milk costs or a tank of gas. He is profoundly out of touch. #p2</t>
+  </si>
+  <si>
+    <t>Romney's pledge to defund Planned Parenthood would remove healthcare from 3 million women. #p2 #Romney</t>
+  </si>
+  <si>
+    <t>Romney said he's not concerned about the very poor. That disqualifies him from the presidency. Full stop. #p2</t>
+  </si>
+  <si>
+    <t>Romney's immigration 'self-deportation' policy is not only cruel, it's economically illiterate. #p2</t>
+  </si>
+  <si>
+    <t>Romney was for the auto bailout before he was against it. His op-ed title was 'Let Detroit Go Bankrupt.' Facts.</t>
+  </si>
+  <si>
+    <t>Romney's 47% comments aren't a gaffe. They're a window into his governing philosophy. Be afraid. #p2</t>
+  </si>
+  <si>
+    <t>2012-03-04</t>
+  </si>
+  <si>
+    <t>Romney's plan to cut the top tax rate to 28% while balancing the budget is mathematically impossible. #p2</t>
+  </si>
+  <si>
+    <t>Romney's education plan would cut Pell Grants and privatize student loans. More debt for students, more profit for banks.</t>
+  </si>
+  <si>
+    <t>Romney vetoed a bill to provide emergency contraception to rape victims as governor. Remember that. #p2</t>
+  </si>
+  <si>
+    <t>Romney says he'd cap government spending at 20% of GDP. Do the math. That means devastating cuts to Medicare. #p2</t>
+  </si>
+  <si>
+    <t>Romney called Russia our number one geopolitical foe in February. He got one thing right accidentally. #p2</t>
+  </si>
+  <si>
+    <t>Romney's opposition to the Lilly Ledbetter Fair Pay Act tells you everything about where his priorities lie. #p2</t>
+  </si>
+  <si>
+    <t>Romney's five sons never served. He had 'opportunities to serve in other ways.' Tell that to Gold Star families.</t>
+  </si>
+  <si>
+    <t>Romney's climate denial is disqualifying. The next president will deal with extreme weather. He won't even name it.</t>
+  </si>
+  <si>
+    <t>Romney's Swiss bank account and Cayman shelters are legal. They're also a window into who he prioritizes. #p2</t>
+  </si>
+  <si>
+    <t>Romney's housing plan: 'let the foreclosure process run its course.' Millions of families disagree. #p2</t>
+  </si>
+  <si>
+    <t>Romney bullied a classmate in high school who was suspected of being gay. His campaign called it 'pranks.' #p2</t>
+  </si>
+  <si>
+    <t>Romney's Medicare voucher plan would shift thousands of dollars in costs onto seniors every year. #p2 #Ryan</t>
+  </si>
+  <si>
+    <t>Romney's embrace of the Ryan budget means cuts to Medicaid that would kick millions off healthcare. Facts. #p2</t>
+  </si>
+  <si>
+    <t>Romney supported Arizona's 'papers please' immigration law. A federal court blocked it as unconstitutional. #p2</t>
+  </si>
+  <si>
+    <t>Romney says he'd 'take a lot of credit' for the auto industry recovery he opposed. Revisionist history. #p2</t>
+  </si>
+  <si>
+    <t>Romney's campaign is run by 22 former Bush administration officials. Same playbook, new face. #p2</t>
+  </si>
+  <si>
+    <t>Romney's opposition to FEMA and federal disaster relief was stated clearly. Sandy shows why that's dangerous.</t>
+  </si>
+  <si>
+    <t>Romney's tax returns from 2009 almost certainly show he used the IRS amnesty for offshore accounts. Disclose. #p2</t>
+  </si>
+  <si>
+    <t>Romney's London Olympics gaffe: questioned whether Britain was ready. They were. He was the embarrassment. #p2</t>
+  </si>
+  <si>
+    <t>Romney's plan to cut foreign aid would devastate global health programs that save millions of lives. #p2</t>
+  </si>
+  <si>
+    <t>Romney's economic plan has been independently scored as adding $5 trillion to the deficit. #p2 #Romney</t>
+  </si>
+  <si>
+    <t>Romney's Jeep ad falsely claimed Chrysler was moving jobs to China. Chrysler CEO called it 'a leap of fantasy.'</t>
+  </si>
+  <si>
+    <t>Romney's response to Sandy Hook — talk about 'turning hearts' — was the emptiest response to a massacre I've heard.</t>
+  </si>
+  <si>
+    <t>Romney's tax plan gives the top 0.1% an average tax cut of $264,000. The math always reveals the priorities. #p2</t>
+  </si>
+  <si>
+    <t>Romney's 'retroactive retirement' from Bain is legal fiction. He was listed as CEO, sole owner, in SEC filings. #p2</t>
+  </si>
+  <si>
+    <t>Romney's promise to repeal DACA on day one would deport 800,000 young Americans who've known no other country.</t>
+  </si>
+  <si>
+    <t>Romney's 47% tape isn't old news. It's the core philosophy of a Romney administration. Don't forget it. #p2</t>
+  </si>
+  <si>
+    <t>Romney's coal ads in Ohio are misleading. The coal industry has been declining for decades. Not Obama's fault.</t>
+  </si>
+  <si>
+    <t>Romney's first act as president would be to sign the Ryan budget. That means gutting Medicare and Medicaid. #p2</t>
+  </si>
+  <si>
+    <t>Romney would appoint Supreme Court justices who would overturn Roe v. Wade. He has said this explicitly. #p2</t>
+  </si>
+  <si>
+    <t>Romney's 'big bird' fixation in the debate revealed a candidate with no serious plan to cut the deficit. #p2</t>
+  </si>
+  <si>
+    <t>Romney's 'self-deportation' immigration plan would tear apart millions of American families. #p2</t>
+  </si>
+  <si>
+    <t>Romney's Ohio Jeep lie was called out by GM and Chrysler directly. He ran the ads anyway. Character test: failed.</t>
+  </si>
+  <si>
+    <t>Romney's 47% remark came up in the debate. He couldn't defend it because it cannot be defended. #p2</t>
+  </si>
+  <si>
+    <t>Romney saying he'd privatize FEMA during a historic hurricane is disqualifying. Disasters need federal response.</t>
+  </si>
+  <si>
+    <t>Romney's closing argument was about Jeeps going to China. PolitiFact: False. That's how he chose to close. #p2</t>
+  </si>
+  <si>
+    <t>Romney's primary instinct to say what crowds want to hear worries me. But his MA record suggests competence.</t>
+  </si>
+  <si>
+    <t>2012-02-13</t>
+  </si>
+  <si>
+    <t>Romney's tax release showed nothing illegal but showed how differently the wealthy are taxed. That's the story.</t>
+  </si>
+  <si>
+    <t>Romney's economic plan has things I like (tax reform) and things I don't (no safety net). Par for the course.</t>
+  </si>
+  <si>
+    <t>Romney's healthcare pivot from MA to national politics exposed a real contradiction. He's never resolved it.</t>
+  </si>
+  <si>
+    <t>Romney is clearly capable and clearly uncomfortable being the 'real' Romney. That tension never goes away.</t>
+  </si>
+  <si>
+    <t>Romney's foreign policy team has some good instincts and some alarming ones. Ryan helps on budget, not on world.</t>
+  </si>
+  <si>
+    <t>Romney's tour abroad was mixed: strong in Israel, disastrous in London, adequate in Poland. Net: below expectations.</t>
+  </si>
+  <si>
+    <t>Ryan pick moves Romney right. That closes the door on the moderate Romney I was hoping to vote for. Reluctant lean Obama.</t>
+  </si>
+  <si>
+    <t>Convention bounce was modest. Romney introduced himself well but still hasn't explained his plan in numbers. #2012</t>
+  </si>
+  <si>
+    <t>Romney won debate 1 on optics. Whether his tax math adds up is a different question. Both things can be true.</t>
+  </si>
+  <si>
+    <t>2012-02-26</t>
+  </si>
+  <si>
+    <t>Romney winning Michigan barely feels like a win. He should dominate his home state. Momentum is not there yet.</t>
+  </si>
+  <si>
+    <t>Romney's 9/11 statement was dignified and appropriate. On this one day I'll give him full credit without caveat.</t>
+  </si>
+  <si>
+    <t>08:11:22</t>
+  </si>
+  <si>
+    <t>Romney said he'd eliminate the Department of Education. That's not reform, that's abandonment of millions of kids. #p2</t>
+  </si>
+  <si>
+    <t>2012-08-31</t>
+  </si>
+  <si>
+    <t>Clint Eastwood at the RNC was bizarre but honestly more memorable than Mitt. That says something. #RNC2012</t>
+  </si>
+  <si>
+    <t>Romney's late surge in the polls is real. Whether it holds through election day is the whole question. #2012</t>
+  </si>
+  <si>
+    <t>Romney's fundraising in Israel while abroad raised conflict-of-interest questions nobody wants to ask. #p2</t>
+  </si>
+  <si>
+    <t>Romney's concession speech was gracious and dignified. Whatever I think of his policies, he handled defeat well.</t>
   </si>
   <si>
     <t>Meaning</t>
@@ -2450,6 +3582,11 @@
       <name val="Arial"/>
     </font>
     <font>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="10.0"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -2458,11 +3595,6 @@
       <sz val="11.0"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -2476,12 +3608,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E79"/>
         <bgColor rgb="FF1F4E79"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor theme="0"/>
       </patternFill>
     </fill>
     <fill>
@@ -2500,6 +3626,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
         <bgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8B1A1A"/>
+        <bgColor rgb="FF8B1A1A"/>
       </patternFill>
     </fill>
   </fills>
@@ -2529,7 +3661,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -2542,60 +3674,69 @@
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="6" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="6" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="6" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="0" fillId="6" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="6" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="6" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="6" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="6" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -2616,6 +3757,10 @@
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2838,18 +3983,19 @@
         <v>2</v>
       </c>
       <c r="E1" s="3"/>
+      <c r="F1" s="4"/>
     </row>
     <row r="2">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="5" t="s">
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="4" t="s">
         <v>5</v>
       </c>
     </row>
@@ -8063,10 +9209,5247 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
-  <sheetData/>
+  <cols>
+    <col customWidth="1" min="1" max="2" width="14.0"/>
+    <col customWidth="1" min="3" max="3" width="12.0"/>
+    <col customWidth="1" min="4" max="4" width="85.0"/>
+    <col customWidth="1" min="5" max="5" width="10.0"/>
+    <col customWidth="1" min="6" max="27" width="8.71"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="21.75" customHeight="1">
+      <c r="A1" s="17"/>
+      <c r="B1" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="19"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11"/>
+      <c r="B3" s="12" t="s">
+        <v>799</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>800</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>801</v>
+      </c>
+      <c r="E3" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8"/>
+      <c r="B4" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>802</v>
+      </c>
+      <c r="E4" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11"/>
+      <c r="B5" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>803</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>804</v>
+      </c>
+      <c r="E5" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8"/>
+      <c r="B6" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>805</v>
+      </c>
+      <c r="E6" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11"/>
+      <c r="B7" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>806</v>
+      </c>
+      <c r="E7" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8"/>
+      <c r="B8" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>698</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>807</v>
+      </c>
+      <c r="E8" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11"/>
+      <c r="B9" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>808</v>
+      </c>
+      <c r="E9" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14"/>
+      <c r="B10" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>797</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>809</v>
+      </c>
+      <c r="E10" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11"/>
+      <c r="B11" s="12" t="s">
+        <v>810</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>811</v>
+      </c>
+      <c r="E11" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8"/>
+      <c r="B12" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>812</v>
+      </c>
+      <c r="E12" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11"/>
+      <c r="B13" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>425</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>813</v>
+      </c>
+      <c r="E13" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8"/>
+      <c r="B14" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>814</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>815</v>
+      </c>
+      <c r="E14" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11"/>
+      <c r="B15" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>816</v>
+      </c>
+      <c r="E15" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8"/>
+      <c r="B16" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>817</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>818</v>
+      </c>
+      <c r="E16" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="14"/>
+      <c r="B17" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>305</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>819</v>
+      </c>
+      <c r="E17" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8"/>
+      <c r="B18" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>820</v>
+      </c>
+      <c r="E18" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11"/>
+      <c r="B19" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>680</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>821</v>
+      </c>
+      <c r="E19" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8"/>
+      <c r="B20" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>712</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>822</v>
+      </c>
+      <c r="E20" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="14"/>
+      <c r="B21" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>402</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>823</v>
+      </c>
+      <c r="E21" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="11"/>
+      <c r="B22" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>539</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>824</v>
+      </c>
+      <c r="E22" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="14"/>
+      <c r="B23" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>825</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>826</v>
+      </c>
+      <c r="E23" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="11"/>
+      <c r="B24" s="12" t="s">
+        <v>827</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>828</v>
+      </c>
+      <c r="E24" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="8"/>
+      <c r="B25" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>829</v>
+      </c>
+      <c r="E25" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="11"/>
+      <c r="B26" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>709</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>830</v>
+      </c>
+      <c r="E26" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="8"/>
+      <c r="B27" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>831</v>
+      </c>
+      <c r="E27" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="8"/>
+      <c r="B28" s="9" t="s">
+        <v>832</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>833</v>
+      </c>
+      <c r="E28" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="14"/>
+      <c r="B29" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D29" s="16" t="s">
+        <v>834</v>
+      </c>
+      <c r="E29" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="11"/>
+      <c r="B30" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>509</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>835</v>
+      </c>
+      <c r="E30" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="8"/>
+      <c r="B31" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>836</v>
+      </c>
+      <c r="E31" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="8"/>
+      <c r="B32" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>837</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>838</v>
+      </c>
+      <c r="E32" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="11"/>
+      <c r="B33" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>839</v>
+      </c>
+      <c r="E33" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="14"/>
+      <c r="B34" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>840</v>
+      </c>
+      <c r="D34" s="16" t="s">
+        <v>841</v>
+      </c>
+      <c r="E34" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="11"/>
+      <c r="B35" s="12" t="s">
+        <v>842</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="D35" s="13" t="s">
+        <v>843</v>
+      </c>
+      <c r="E35" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="A36" s="8"/>
+      <c r="B36" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>844</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>845</v>
+      </c>
+      <c r="E36" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="37" ht="15.75" customHeight="1">
+      <c r="A37" s="14"/>
+      <c r="B37" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="D37" s="16" t="s">
+        <v>846</v>
+      </c>
+      <c r="E37" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="38" ht="15.75" customHeight="1">
+      <c r="A38" s="11"/>
+      <c r="B38" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>847</v>
+      </c>
+      <c r="D38" s="13" t="s">
+        <v>848</v>
+      </c>
+      <c r="E38" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="39" ht="15.75" customHeight="1">
+      <c r="A39" s="14"/>
+      <c r="B39" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>712</v>
+      </c>
+      <c r="D39" s="16" t="s">
+        <v>849</v>
+      </c>
+      <c r="E39" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="40" ht="15.75" customHeight="1">
+      <c r="A40" s="8"/>
+      <c r="B40" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="D40" s="10" t="s">
+        <v>850</v>
+      </c>
+      <c r="E40" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="41" ht="15.75" customHeight="1">
+      <c r="A41" s="11"/>
+      <c r="B41" s="12" t="s">
+        <v>851</v>
+      </c>
+      <c r="C41" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="D41" s="13" t="s">
+        <v>852</v>
+      </c>
+      <c r="E41" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="42" ht="15.75" customHeight="1">
+      <c r="A42" s="14"/>
+      <c r="B42" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="C42" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D42" s="16" t="s">
+        <v>853</v>
+      </c>
+      <c r="E42" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="43" ht="15.75" customHeight="1">
+      <c r="A43" s="8"/>
+      <c r="B43" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>854</v>
+      </c>
+      <c r="E43" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="44" ht="15.75" customHeight="1">
+      <c r="A44" s="8"/>
+      <c r="B44" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="D44" s="10" t="s">
+        <v>855</v>
+      </c>
+      <c r="E44" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="45" ht="15.75" customHeight="1">
+      <c r="A45" s="11"/>
+      <c r="B45" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="C45" s="12" t="s">
+        <v>856</v>
+      </c>
+      <c r="D45" s="13" t="s">
+        <v>857</v>
+      </c>
+      <c r="E45" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="46" ht="15.75" customHeight="1">
+      <c r="A46" s="11"/>
+      <c r="B46" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="C46" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="D46" s="13" t="s">
+        <v>858</v>
+      </c>
+      <c r="E46" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="47" ht="15.75" customHeight="1">
+      <c r="A47" s="8"/>
+      <c r="B47" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="D47" s="10" t="s">
+        <v>859</v>
+      </c>
+      <c r="E47" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="48" ht="15.75" customHeight="1">
+      <c r="A48" s="8"/>
+      <c r="B48" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>860</v>
+      </c>
+      <c r="D48" s="10" t="s">
+        <v>861</v>
+      </c>
+      <c r="E48" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="49" ht="15.75" customHeight="1">
+      <c r="A49" s="11"/>
+      <c r="B49" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="C49" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="D49" s="13" t="s">
+        <v>862</v>
+      </c>
+      <c r="E49" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="50" ht="15.75" customHeight="1">
+      <c r="A50" s="14"/>
+      <c r="B50" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="C50" s="15" t="s">
+        <v>582</v>
+      </c>
+      <c r="D50" s="16" t="s">
+        <v>863</v>
+      </c>
+      <c r="E50" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="51" ht="15.75" customHeight="1">
+      <c r="A51" s="11"/>
+      <c r="B51" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="C51" s="12" t="s">
+        <v>606</v>
+      </c>
+      <c r="D51" s="13" t="s">
+        <v>864</v>
+      </c>
+      <c r="E51" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="52" ht="15.75" customHeight="1">
+      <c r="A52" s="8"/>
+      <c r="B52" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>825</v>
+      </c>
+      <c r="D52" s="10" t="s">
+        <v>865</v>
+      </c>
+      <c r="E52" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="53" ht="15.75" customHeight="1">
+      <c r="A53" s="8"/>
+      <c r="B53" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>866</v>
+      </c>
+      <c r="D53" s="10" t="s">
+        <v>867</v>
+      </c>
+      <c r="E53" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="54" ht="15.75" customHeight="1">
+      <c r="A54" s="11"/>
+      <c r="B54" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="C54" s="12" t="s">
+        <v>868</v>
+      </c>
+      <c r="D54" s="13" t="s">
+        <v>869</v>
+      </c>
+      <c r="E54" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="55" ht="15.75" customHeight="1">
+      <c r="A55" s="11"/>
+      <c r="B55" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="C55" s="12" t="s">
+        <v>870</v>
+      </c>
+      <c r="D55" s="13" t="s">
+        <v>871</v>
+      </c>
+      <c r="E55" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="56" ht="15.75" customHeight="1">
+      <c r="A56" s="8"/>
+      <c r="B56" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="C56" s="9" t="s">
+        <v>872</v>
+      </c>
+      <c r="D56" s="10" t="s">
+        <v>873</v>
+      </c>
+      <c r="E56" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="57" ht="15.75" customHeight="1">
+      <c r="A57" s="14"/>
+      <c r="B57" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="C57" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="D57" s="16" t="s">
+        <v>874</v>
+      </c>
+      <c r="E57" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="58" ht="15.75" customHeight="1">
+      <c r="A58" s="11"/>
+      <c r="B58" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="C58" s="12" t="s">
+        <v>875</v>
+      </c>
+      <c r="D58" s="13" t="s">
+        <v>876</v>
+      </c>
+      <c r="E58" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="59" ht="15.75" customHeight="1">
+      <c r="A59" s="14"/>
+      <c r="B59" s="15" t="s">
+        <v>877</v>
+      </c>
+      <c r="C59" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="D59" s="16" t="s">
+        <v>878</v>
+      </c>
+      <c r="E59" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="60" ht="15.75" customHeight="1">
+      <c r="A60" s="8"/>
+      <c r="B60" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="C60" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D60" s="10" t="s">
+        <v>879</v>
+      </c>
+      <c r="E60" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="61" ht="15.75" customHeight="1">
+      <c r="A61" s="11"/>
+      <c r="B61" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="C61" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="D61" s="13" t="s">
+        <v>880</v>
+      </c>
+      <c r="E61" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="62" ht="15.75" customHeight="1">
+      <c r="A62" s="14"/>
+      <c r="B62" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="C62" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="D62" s="16" t="s">
+        <v>881</v>
+      </c>
+      <c r="E62" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="63" ht="15.75" customHeight="1">
+      <c r="A63" s="8"/>
+      <c r="B63" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="C63" s="9" t="s">
+        <v>882</v>
+      </c>
+      <c r="D63" s="10" t="s">
+        <v>883</v>
+      </c>
+      <c r="E63" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="64" ht="15.75" customHeight="1">
+      <c r="A64" s="8"/>
+      <c r="B64" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="C64" s="9" t="s">
+        <v>840</v>
+      </c>
+      <c r="D64" s="10" t="s">
+        <v>884</v>
+      </c>
+      <c r="E64" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="65" ht="15.75" customHeight="1">
+      <c r="A65" s="11"/>
+      <c r="B65" s="12" t="s">
+        <v>885</v>
+      </c>
+      <c r="C65" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="D65" s="13" t="s">
+        <v>886</v>
+      </c>
+      <c r="E65" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="66" ht="15.75" customHeight="1">
+      <c r="A66" s="11"/>
+      <c r="B66" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="C66" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="D66" s="13" t="s">
+        <v>887</v>
+      </c>
+      <c r="E66" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="67" ht="15.75" customHeight="1">
+      <c r="A67" s="14"/>
+      <c r="B67" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="C67" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="D67" s="16" t="s">
+        <v>888</v>
+      </c>
+      <c r="E67" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="68" ht="15.75" customHeight="1">
+      <c r="A68" s="8"/>
+      <c r="B68" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="C68" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D68" s="10" t="s">
+        <v>889</v>
+      </c>
+      <c r="E68" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="69" ht="15.75" customHeight="1">
+      <c r="A69" s="11"/>
+      <c r="B69" s="12" t="s">
+        <v>251</v>
+      </c>
+      <c r="C69" s="12" t="s">
+        <v>509</v>
+      </c>
+      <c r="D69" s="13" t="s">
+        <v>890</v>
+      </c>
+      <c r="E69" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="70" ht="15.75" customHeight="1">
+      <c r="A70" s="8"/>
+      <c r="B70" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="C70" s="9" t="s">
+        <v>891</v>
+      </c>
+      <c r="D70" s="10" t="s">
+        <v>892</v>
+      </c>
+      <c r="E70" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="71" ht="15.75" customHeight="1">
+      <c r="A71" s="14"/>
+      <c r="B71" s="15" t="s">
+        <v>265</v>
+      </c>
+      <c r="C71" s="15" t="s">
+        <v>893</v>
+      </c>
+      <c r="D71" s="16" t="s">
+        <v>894</v>
+      </c>
+      <c r="E71" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="72" ht="15.75" customHeight="1">
+      <c r="A72" s="8"/>
+      <c r="B72" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="C72" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="D72" s="10" t="s">
+        <v>895</v>
+      </c>
+      <c r="E72" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="73" ht="15.75" customHeight="1">
+      <c r="A73" s="11"/>
+      <c r="B73" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="C73" s="12" t="s">
+        <v>539</v>
+      </c>
+      <c r="D73" s="13" t="s">
+        <v>896</v>
+      </c>
+      <c r="E73" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="74" ht="15.75" customHeight="1">
+      <c r="A74" s="8"/>
+      <c r="B74" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="C74" s="9" t="s">
+        <v>897</v>
+      </c>
+      <c r="D74" s="10" t="s">
+        <v>898</v>
+      </c>
+      <c r="E74" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="75" ht="15.75" customHeight="1">
+      <c r="A75" s="11"/>
+      <c r="B75" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="C75" s="12" t="s">
+        <v>899</v>
+      </c>
+      <c r="D75" s="13" t="s">
+        <v>900</v>
+      </c>
+      <c r="E75" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="76" ht="15.75" customHeight="1">
+      <c r="A76" s="14"/>
+      <c r="B76" s="15" t="s">
+        <v>282</v>
+      </c>
+      <c r="C76" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="D76" s="16" t="s">
+        <v>902</v>
+      </c>
+      <c r="E76" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="77" ht="15.75" customHeight="1">
+      <c r="A77" s="8"/>
+      <c r="B77" s="9" t="s">
+        <v>903</v>
+      </c>
+      <c r="C77" s="9" t="s">
+        <v>904</v>
+      </c>
+      <c r="D77" s="10" t="s">
+        <v>905</v>
+      </c>
+      <c r="E77" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="78" ht="15.75" customHeight="1">
+      <c r="A78" s="11"/>
+      <c r="B78" s="12" t="s">
+        <v>288</v>
+      </c>
+      <c r="C78" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="D78" s="13" t="s">
+        <v>906</v>
+      </c>
+      <c r="E78" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="79" ht="15.75" customHeight="1">
+      <c r="A79" s="14"/>
+      <c r="B79" s="15" t="s">
+        <v>294</v>
+      </c>
+      <c r="C79" s="15" t="s">
+        <v>907</v>
+      </c>
+      <c r="D79" s="16" t="s">
+        <v>908</v>
+      </c>
+      <c r="E79" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="80" ht="15.75" customHeight="1">
+      <c r="A80" s="8"/>
+      <c r="B80" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="C80" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D80" s="10" t="s">
+        <v>909</v>
+      </c>
+      <c r="E80" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="81" ht="15.75" customHeight="1">
+      <c r="A81" s="11"/>
+      <c r="B81" s="12" t="s">
+        <v>307</v>
+      </c>
+      <c r="C81" s="12" t="s">
+        <v>910</v>
+      </c>
+      <c r="D81" s="13" t="s">
+        <v>911</v>
+      </c>
+      <c r="E81" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="82" ht="15.75" customHeight="1">
+      <c r="A82" s="8"/>
+      <c r="B82" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="C82" s="9" t="s">
+        <v>912</v>
+      </c>
+      <c r="D82" s="10" t="s">
+        <v>913</v>
+      </c>
+      <c r="E82" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="83" ht="15.75" customHeight="1">
+      <c r="A83" s="14"/>
+      <c r="B83" s="15" t="s">
+        <v>314</v>
+      </c>
+      <c r="C83" s="15" t="s">
+        <v>683</v>
+      </c>
+      <c r="D83" s="16" t="s">
+        <v>914</v>
+      </c>
+      <c r="E83" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="84" ht="15.75" customHeight="1">
+      <c r="A84" s="8"/>
+      <c r="B84" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="C84" s="9" t="s">
+        <v>915</v>
+      </c>
+      <c r="D84" s="10" t="s">
+        <v>916</v>
+      </c>
+      <c r="E84" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="85" ht="15.75" customHeight="1">
+      <c r="A85" s="8"/>
+      <c r="B85" s="9" t="s">
+        <v>917</v>
+      </c>
+      <c r="C85" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D85" s="10" t="s">
+        <v>918</v>
+      </c>
+      <c r="E85" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="86" ht="15.75" customHeight="1">
+      <c r="A86" s="11"/>
+      <c r="B86" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="C86" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="D86" s="13" t="s">
+        <v>919</v>
+      </c>
+      <c r="E86" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="87" ht="15.75" customHeight="1">
+      <c r="A87" s="11"/>
+      <c r="B87" s="12" t="s">
+        <v>920</v>
+      </c>
+      <c r="C87" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="D87" s="13" t="s">
+        <v>921</v>
+      </c>
+      <c r="E87" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="88" ht="15.75" customHeight="1">
+      <c r="A88" s="8"/>
+      <c r="B88" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="C88" s="9" t="s">
+        <v>582</v>
+      </c>
+      <c r="D88" s="10" t="s">
+        <v>922</v>
+      </c>
+      <c r="E88" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="89" ht="15.75" customHeight="1">
+      <c r="A89" s="11"/>
+      <c r="B89" s="12" t="s">
+        <v>923</v>
+      </c>
+      <c r="C89" s="12" t="s">
+        <v>837</v>
+      </c>
+      <c r="D89" s="13" t="s">
+        <v>924</v>
+      </c>
+      <c r="E89" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="90" ht="15.75" customHeight="1">
+      <c r="A90" s="11"/>
+      <c r="B90" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="C90" s="12" t="s">
+        <v>628</v>
+      </c>
+      <c r="D90" s="13" t="s">
+        <v>925</v>
+      </c>
+      <c r="E90" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="91" ht="15.75" customHeight="1">
+      <c r="A91" s="14"/>
+      <c r="B91" s="15" t="s">
+        <v>347</v>
+      </c>
+      <c r="C91" s="15" t="s">
+        <v>926</v>
+      </c>
+      <c r="D91" s="16" t="s">
+        <v>927</v>
+      </c>
+      <c r="E91" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="92" ht="15.75" customHeight="1">
+      <c r="A92" s="8"/>
+      <c r="B92" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="C92" s="9" t="s">
+        <v>928</v>
+      </c>
+      <c r="D92" s="10" t="s">
+        <v>929</v>
+      </c>
+      <c r="E92" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="93" ht="15.75" customHeight="1">
+      <c r="A93" s="8"/>
+      <c r="B93" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="C93" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="D93" s="10" t="s">
+        <v>930</v>
+      </c>
+      <c r="E93" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="94" ht="15.75" customHeight="1">
+      <c r="A94" s="11"/>
+      <c r="B94" s="12" t="s">
+        <v>931</v>
+      </c>
+      <c r="C94" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="D94" s="13" t="s">
+        <v>932</v>
+      </c>
+      <c r="E94" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="95" ht="15.75" customHeight="1">
+      <c r="A95" s="14"/>
+      <c r="B95" s="15" t="s">
+        <v>364</v>
+      </c>
+      <c r="C95" s="15" t="s">
+        <v>422</v>
+      </c>
+      <c r="D95" s="16" t="s">
+        <v>933</v>
+      </c>
+      <c r="E95" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="96" ht="15.75" customHeight="1">
+      <c r="A96" s="8"/>
+      <c r="B96" s="9" t="s">
+        <v>367</v>
+      </c>
+      <c r="C96" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="D96" s="10" t="s">
+        <v>934</v>
+      </c>
+      <c r="E96" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="97" ht="15.75" customHeight="1">
+      <c r="A97" s="11"/>
+      <c r="B97" s="12" t="s">
+        <v>935</v>
+      </c>
+      <c r="C97" s="12" t="s">
+        <v>936</v>
+      </c>
+      <c r="D97" s="13" t="s">
+        <v>937</v>
+      </c>
+      <c r="E97" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="98" ht="15.75" customHeight="1">
+      <c r="A98" s="8"/>
+      <c r="B98" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="C98" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="D98" s="10" t="s">
+        <v>938</v>
+      </c>
+      <c r="E98" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="99" ht="15.75" customHeight="1">
+      <c r="A99" s="14"/>
+      <c r="B99" s="15" t="s">
+        <v>379</v>
+      </c>
+      <c r="C99" s="15" t="s">
+        <v>449</v>
+      </c>
+      <c r="D99" s="16" t="s">
+        <v>939</v>
+      </c>
+      <c r="E99" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="100" ht="15.75" customHeight="1">
+      <c r="A100" s="8"/>
+      <c r="B100" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="C100" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="D100" s="10" t="s">
+        <v>940</v>
+      </c>
+      <c r="E100" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="101" ht="15.75" customHeight="1">
+      <c r="A101" s="11"/>
+      <c r="B101" s="12" t="s">
+        <v>388</v>
+      </c>
+      <c r="C101" s="12" t="s">
+        <v>941</v>
+      </c>
+      <c r="D101" s="13" t="s">
+        <v>942</v>
+      </c>
+      <c r="E101" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="102" ht="15.75" customHeight="1">
+      <c r="A102" s="8"/>
+      <c r="B102" s="9" t="s">
+        <v>395</v>
+      </c>
+      <c r="C102" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="D102" s="10" t="s">
+        <v>943</v>
+      </c>
+      <c r="E102" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="103" ht="15.75" customHeight="1">
+      <c r="A103" s="8"/>
+      <c r="B103" s="9" t="s">
+        <v>944</v>
+      </c>
+      <c r="C103" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="D103" s="10" t="s">
+        <v>945</v>
+      </c>
+      <c r="E103" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="104" ht="15.75" customHeight="1">
+      <c r="A104" s="11"/>
+      <c r="B104" s="12" t="s">
+        <v>398</v>
+      </c>
+      <c r="C104" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="D104" s="13" t="s">
+        <v>946</v>
+      </c>
+      <c r="E104" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="105" ht="15.75" customHeight="1">
+      <c r="A105" s="14"/>
+      <c r="B105" s="15" t="s">
+        <v>401</v>
+      </c>
+      <c r="C105" s="15" t="s">
+        <v>947</v>
+      </c>
+      <c r="D105" s="16" t="s">
+        <v>948</v>
+      </c>
+      <c r="E105" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="106" ht="15.75" customHeight="1">
+      <c r="A106" s="14"/>
+      <c r="B106" s="15" t="s">
+        <v>410</v>
+      </c>
+      <c r="C106" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D106" s="16" t="s">
+        <v>949</v>
+      </c>
+      <c r="E106" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="107" ht="15.75" customHeight="1">
+      <c r="A107" s="11"/>
+      <c r="B107" s="12" t="s">
+        <v>412</v>
+      </c>
+      <c r="C107" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="D107" s="13" t="s">
+        <v>950</v>
+      </c>
+      <c r="E107" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="108" ht="15.75" customHeight="1">
+      <c r="A108" s="8"/>
+      <c r="B108" s="9" t="s">
+        <v>415</v>
+      </c>
+      <c r="C108" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="D108" s="10" t="s">
+        <v>951</v>
+      </c>
+      <c r="E108" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="109" ht="15.75" customHeight="1">
+      <c r="A109" s="11"/>
+      <c r="B109" s="12" t="s">
+        <v>418</v>
+      </c>
+      <c r="C109" s="12" t="s">
+        <v>952</v>
+      </c>
+      <c r="D109" s="13" t="s">
+        <v>953</v>
+      </c>
+      <c r="E109" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="110" ht="15.75" customHeight="1">
+      <c r="A110" s="11"/>
+      <c r="B110" s="12" t="s">
+        <v>427</v>
+      </c>
+      <c r="C110" s="12" t="s">
+        <v>954</v>
+      </c>
+      <c r="D110" s="13" t="s">
+        <v>955</v>
+      </c>
+      <c r="E110" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="111" ht="15.75" customHeight="1">
+      <c r="A111" s="8"/>
+      <c r="B111" s="9" t="s">
+        <v>433</v>
+      </c>
+      <c r="C111" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="D111" s="10" t="s">
+        <v>956</v>
+      </c>
+      <c r="E111" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="112" ht="15.75" customHeight="1">
+      <c r="A112" s="11"/>
+      <c r="B112" s="12" t="s">
+        <v>436</v>
+      </c>
+      <c r="C112" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="D112" s="13" t="s">
+        <v>957</v>
+      </c>
+      <c r="E112" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="113" ht="15.75" customHeight="1">
+      <c r="A113" s="14"/>
+      <c r="B113" s="15" t="s">
+        <v>440</v>
+      </c>
+      <c r="C113" s="15" t="s">
+        <v>295</v>
+      </c>
+      <c r="D113" s="16" t="s">
+        <v>958</v>
+      </c>
+      <c r="E113" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="114" ht="15.75" customHeight="1">
+      <c r="A114" s="14"/>
+      <c r="B114" s="15" t="s">
+        <v>448</v>
+      </c>
+      <c r="C114" s="15" t="s">
+        <v>860</v>
+      </c>
+      <c r="D114" s="16" t="s">
+        <v>959</v>
+      </c>
+      <c r="E114" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="115" ht="15.75" customHeight="1">
+      <c r="A115" s="8"/>
+      <c r="B115" s="9" t="s">
+        <v>451</v>
+      </c>
+      <c r="C115" s="9" t="s">
+        <v>825</v>
+      </c>
+      <c r="D115" s="10" t="s">
+        <v>960</v>
+      </c>
+      <c r="E115" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="116" ht="15.75" customHeight="1">
+      <c r="A116" s="11"/>
+      <c r="B116" s="12" t="s">
+        <v>456</v>
+      </c>
+      <c r="C116" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="D116" s="13" t="s">
+        <v>961</v>
+      </c>
+      <c r="E116" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="117" ht="15.75" customHeight="1">
+      <c r="A117" s="11"/>
+      <c r="B117" s="12" t="s">
+        <v>464</v>
+      </c>
+      <c r="C117" s="12" t="s">
+        <v>962</v>
+      </c>
+      <c r="D117" s="13" t="s">
+        <v>963</v>
+      </c>
+      <c r="E117" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="118" ht="15.75" customHeight="1">
+      <c r="A118" s="8"/>
+      <c r="B118" s="9" t="s">
+        <v>467</v>
+      </c>
+      <c r="C118" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="D118" s="10" t="s">
+        <v>964</v>
+      </c>
+      <c r="E118" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="119" ht="15.75" customHeight="1">
+      <c r="A119" s="8"/>
+      <c r="B119" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="C119" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="D119" s="10" t="s">
+        <v>965</v>
+      </c>
+      <c r="E119" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="120" ht="15.75" customHeight="1">
+      <c r="A120" s="11"/>
+      <c r="B120" s="12" t="s">
+        <v>475</v>
+      </c>
+      <c r="C120" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="D120" s="13" t="s">
+        <v>966</v>
+      </c>
+      <c r="E120" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="121" ht="15.75" customHeight="1">
+      <c r="A121" s="11"/>
+      <c r="B121" s="12" t="s">
+        <v>479</v>
+      </c>
+      <c r="C121" s="12" t="s">
+        <v>947</v>
+      </c>
+      <c r="D121" s="13" t="s">
+        <v>967</v>
+      </c>
+      <c r="E121" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="122" ht="15.75" customHeight="1">
+      <c r="A122" s="14"/>
+      <c r="B122" s="15" t="s">
+        <v>485</v>
+      </c>
+      <c r="C122" s="15" t="s">
+        <v>825</v>
+      </c>
+      <c r="D122" s="16" t="s">
+        <v>968</v>
+      </c>
+      <c r="E122" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="123" ht="15.75" customHeight="1">
+      <c r="A123" s="8"/>
+      <c r="B123" s="9" t="s">
+        <v>488</v>
+      </c>
+      <c r="C123" s="9" t="s">
+        <v>489</v>
+      </c>
+      <c r="D123" s="10" t="s">
+        <v>969</v>
+      </c>
+      <c r="E123" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="124" ht="15.75" customHeight="1">
+      <c r="A124" s="8"/>
+      <c r="B124" s="9" t="s">
+        <v>491</v>
+      </c>
+      <c r="C124" s="9" t="s">
+        <v>970</v>
+      </c>
+      <c r="D124" s="10" t="s">
+        <v>971</v>
+      </c>
+      <c r="E124" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="125" ht="15.75" customHeight="1">
+      <c r="A125" s="11"/>
+      <c r="B125" s="12" t="s">
+        <v>493</v>
+      </c>
+      <c r="C125" s="12" t="s">
+        <v>972</v>
+      </c>
+      <c r="D125" s="13" t="s">
+        <v>973</v>
+      </c>
+      <c r="E125" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="126" ht="15.75" customHeight="1">
+      <c r="A126" s="14"/>
+      <c r="B126" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="C126" s="15" t="s">
+        <v>840</v>
+      </c>
+      <c r="D126" s="16" t="s">
+        <v>974</v>
+      </c>
+      <c r="E126" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="127" ht="15.75" customHeight="1">
+      <c r="A127" s="8"/>
+      <c r="B127" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="C127" s="9" t="s">
+        <v>868</v>
+      </c>
+      <c r="D127" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="E127" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="128" ht="15.75" customHeight="1">
+      <c r="A128" s="11"/>
+      <c r="B128" s="12" t="s">
+        <v>508</v>
+      </c>
+      <c r="C128" s="12" t="s">
+        <v>976</v>
+      </c>
+      <c r="D128" s="13" t="s">
+        <v>977</v>
+      </c>
+      <c r="E128" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="129" ht="15.75" customHeight="1">
+      <c r="A129" s="14"/>
+      <c r="B129" s="15" t="s">
+        <v>518</v>
+      </c>
+      <c r="C129" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="D129" s="16" t="s">
+        <v>978</v>
+      </c>
+      <c r="E129" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="130" ht="15.75" customHeight="1">
+      <c r="A130" s="14"/>
+      <c r="B130" s="15" t="s">
+        <v>520</v>
+      </c>
+      <c r="C130" s="15" t="s">
+        <v>521</v>
+      </c>
+      <c r="D130" s="16" t="s">
+        <v>979</v>
+      </c>
+      <c r="E130" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="131" ht="15.75" customHeight="1">
+      <c r="A131" s="8"/>
+      <c r="B131" s="9" t="s">
+        <v>523</v>
+      </c>
+      <c r="C131" s="9" t="s">
+        <v>524</v>
+      </c>
+      <c r="D131" s="10" t="s">
+        <v>980</v>
+      </c>
+      <c r="E131" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="132" ht="15.75" customHeight="1">
+      <c r="A132" s="8"/>
+      <c r="B132" s="9" t="s">
+        <v>523</v>
+      </c>
+      <c r="C132" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D132" s="10" t="s">
+        <v>981</v>
+      </c>
+      <c r="E132" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="133" ht="15.75" customHeight="1">
+      <c r="A133" s="11"/>
+      <c r="B133" s="12" t="s">
+        <v>528</v>
+      </c>
+      <c r="C133" s="12" t="s">
+        <v>860</v>
+      </c>
+      <c r="D133" s="13" t="s">
+        <v>982</v>
+      </c>
+      <c r="E133" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="134" ht="15.75" customHeight="1">
+      <c r="A134" s="11"/>
+      <c r="B134" s="12" t="s">
+        <v>532</v>
+      </c>
+      <c r="C134" s="12" t="s">
+        <v>983</v>
+      </c>
+      <c r="D134" s="13" t="s">
+        <v>984</v>
+      </c>
+      <c r="E134" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="135" ht="15.75" customHeight="1">
+      <c r="A135" s="14"/>
+      <c r="B135" s="15" t="s">
+        <v>538</v>
+      </c>
+      <c r="C135" s="15" t="s">
+        <v>860</v>
+      </c>
+      <c r="D135" s="16" t="s">
+        <v>985</v>
+      </c>
+      <c r="E135" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="136" ht="15.75" customHeight="1">
+      <c r="A136" s="8"/>
+      <c r="B136" s="9" t="s">
+        <v>544</v>
+      </c>
+      <c r="C136" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D136" s="10" t="s">
+        <v>986</v>
+      </c>
+      <c r="E136" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="137" ht="15.75" customHeight="1">
+      <c r="A137" s="11"/>
+      <c r="B137" s="12" t="s">
+        <v>547</v>
+      </c>
+      <c r="C137" s="12" t="s">
+        <v>797</v>
+      </c>
+      <c r="D137" s="13" t="s">
+        <v>987</v>
+      </c>
+      <c r="E137" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="138" ht="15.75" customHeight="1">
+      <c r="A138" s="11"/>
+      <c r="B138" s="12" t="s">
+        <v>553</v>
+      </c>
+      <c r="C138" s="12" t="s">
+        <v>910</v>
+      </c>
+      <c r="D138" s="13" t="s">
+        <v>988</v>
+      </c>
+      <c r="E138" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="139" ht="15.75" customHeight="1">
+      <c r="A139" s="8"/>
+      <c r="B139" s="9" t="s">
+        <v>989</v>
+      </c>
+      <c r="C139" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="D139" s="10" t="s">
+        <v>990</v>
+      </c>
+      <c r="E139" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="140" ht="15.75" customHeight="1">
+      <c r="A140" s="8"/>
+      <c r="B140" s="9" t="s">
+        <v>560</v>
+      </c>
+      <c r="C140" s="9" t="s">
+        <v>991</v>
+      </c>
+      <c r="D140" s="10" t="s">
+        <v>992</v>
+      </c>
+      <c r="E140" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="141" ht="15.75" customHeight="1">
+      <c r="A141" s="11"/>
+      <c r="B141" s="12" t="s">
+        <v>563</v>
+      </c>
+      <c r="C141" s="12" t="s">
+        <v>377</v>
+      </c>
+      <c r="D141" s="13" t="s">
+        <v>993</v>
+      </c>
+      <c r="E141" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="142" ht="15.75" customHeight="1">
+      <c r="A142" s="14"/>
+      <c r="B142" s="15" t="s">
+        <v>573</v>
+      </c>
+      <c r="C142" s="15" t="s">
+        <v>449</v>
+      </c>
+      <c r="D142" s="16" t="s">
+        <v>994</v>
+      </c>
+      <c r="E142" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="143" ht="15.75" customHeight="1">
+      <c r="A143" s="11"/>
+      <c r="B143" s="12" t="s">
+        <v>576</v>
+      </c>
+      <c r="C143" s="12" t="s">
+        <v>298</v>
+      </c>
+      <c r="D143" s="13" t="s">
+        <v>995</v>
+      </c>
+      <c r="E143" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="144" ht="15.75" customHeight="1">
+      <c r="A144" s="8"/>
+      <c r="B144" s="9" t="s">
+        <v>576</v>
+      </c>
+      <c r="C144" s="9" t="s">
+        <v>574</v>
+      </c>
+      <c r="D144" s="10" t="s">
+        <v>996</v>
+      </c>
+      <c r="E144" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="145" ht="15.75" customHeight="1">
+      <c r="A145" s="8"/>
+      <c r="B145" s="9" t="s">
+        <v>578</v>
+      </c>
+      <c r="C145" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="D145" s="10" t="s">
+        <v>997</v>
+      </c>
+      <c r="E145" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="146" ht="15.75" customHeight="1">
+      <c r="A146" s="11"/>
+      <c r="B146" s="12" t="s">
+        <v>581</v>
+      </c>
+      <c r="C146" s="12" t="s">
+        <v>539</v>
+      </c>
+      <c r="D146" s="13" t="s">
+        <v>998</v>
+      </c>
+      <c r="E146" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="147" ht="15.75" customHeight="1">
+      <c r="A147" s="14"/>
+      <c r="B147" s="15" t="s">
+        <v>596</v>
+      </c>
+      <c r="C147" s="15" t="s">
+        <v>717</v>
+      </c>
+      <c r="D147" s="16" t="s">
+        <v>999</v>
+      </c>
+      <c r="E147" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="148" ht="15.75" customHeight="1">
+      <c r="A148" s="8"/>
+      <c r="B148" s="9" t="s">
+        <v>598</v>
+      </c>
+      <c r="C148" s="9" t="s">
+        <v>825</v>
+      </c>
+      <c r="D148" s="10" t="s">
+        <v>1000</v>
+      </c>
+      <c r="E148" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="149" ht="15.75" customHeight="1">
+      <c r="A149" s="11"/>
+      <c r="B149" s="12" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C149" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="D149" s="13" t="s">
+        <v>1002</v>
+      </c>
+      <c r="E149" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="150" ht="15.75" customHeight="1">
+      <c r="A150" s="8"/>
+      <c r="B150" s="9" t="s">
+        <v>602</v>
+      </c>
+      <c r="C150" s="9" t="s">
+        <v>603</v>
+      </c>
+      <c r="D150" s="10" t="s">
+        <v>1003</v>
+      </c>
+      <c r="E150" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="151" ht="15.75" customHeight="1">
+      <c r="A151" s="14"/>
+      <c r="B151" s="15" t="s">
+        <v>605</v>
+      </c>
+      <c r="C151" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D151" s="16" t="s">
+        <v>1004</v>
+      </c>
+      <c r="E151" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="152" ht="15.75" customHeight="1">
+      <c r="A152" s="8"/>
+      <c r="B152" s="9" t="s">
+        <v>608</v>
+      </c>
+      <c r="C152" s="9" t="s">
+        <v>425</v>
+      </c>
+      <c r="D152" s="10" t="s">
+        <v>1005</v>
+      </c>
+      <c r="E152" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="153" ht="15.75" customHeight="1">
+      <c r="A153" s="11"/>
+      <c r="B153" s="12" t="s">
+        <v>610</v>
+      </c>
+      <c r="C153" s="12" t="s">
+        <v>425</v>
+      </c>
+      <c r="D153" s="13" t="s">
+        <v>1006</v>
+      </c>
+      <c r="E153" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="154" ht="15.75" customHeight="1">
+      <c r="A154" s="8"/>
+      <c r="B154" s="9" t="s">
+        <v>615</v>
+      </c>
+      <c r="C154" s="9" t="s">
+        <v>712</v>
+      </c>
+      <c r="D154" s="10" t="s">
+        <v>1007</v>
+      </c>
+      <c r="E154" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="155" ht="15.75" customHeight="1">
+      <c r="A155" s="11"/>
+      <c r="B155" s="12" t="s">
+        <v>619</v>
+      </c>
+      <c r="C155" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="D155" s="13" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E155" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="156" ht="15.75" customHeight="1">
+      <c r="A156" s="8"/>
+      <c r="B156" s="9" t="s">
+        <v>627</v>
+      </c>
+      <c r="C156" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D156" s="10" t="s">
+        <v>1009</v>
+      </c>
+      <c r="E156" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="157" ht="15.75" customHeight="1">
+      <c r="A157" s="11"/>
+      <c r="B157" s="12" t="s">
+        <v>630</v>
+      </c>
+      <c r="C157" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D157" s="13" t="s">
+        <v>1010</v>
+      </c>
+      <c r="E157" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="158" ht="15.75" customHeight="1">
+      <c r="A158" s="14"/>
+      <c r="B158" s="15" t="s">
+        <v>633</v>
+      </c>
+      <c r="C158" s="15" t="s">
+        <v>628</v>
+      </c>
+      <c r="D158" s="16" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E158" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="159" ht="15.75" customHeight="1">
+      <c r="A159" s="11"/>
+      <c r="B159" s="12" t="s">
+        <v>637</v>
+      </c>
+      <c r="C159" s="12" t="s">
+        <v>342</v>
+      </c>
+      <c r="D159" s="13" t="s">
+        <v>1012</v>
+      </c>
+      <c r="E159" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="160" ht="15.75" customHeight="1">
+      <c r="A160" s="14"/>
+      <c r="B160" s="15" t="s">
+        <v>641</v>
+      </c>
+      <c r="C160" s="15" t="s">
+        <v>926</v>
+      </c>
+      <c r="D160" s="16" t="s">
+        <v>1013</v>
+      </c>
+      <c r="E160" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="161" ht="15.75" customHeight="1">
+      <c r="A161" s="8"/>
+      <c r="B161" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C161" s="9" t="s">
+        <v>868</v>
+      </c>
+      <c r="D161" s="10" t="s">
+        <v>1014</v>
+      </c>
+      <c r="E161" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="162" ht="15.75" customHeight="1">
+      <c r="A162" s="11"/>
+      <c r="B162" s="12" t="s">
+        <v>647</v>
+      </c>
+      <c r="C162" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D162" s="13" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E162" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="163" ht="15.75" customHeight="1">
+      <c r="A163" s="8"/>
+      <c r="B163" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="C163" s="9" t="s">
+        <v>651</v>
+      </c>
+      <c r="D163" s="10" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E163" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="164" ht="15.75" customHeight="1">
+      <c r="A164" s="14"/>
+      <c r="B164" s="15" t="s">
+        <v>660</v>
+      </c>
+      <c r="C164" s="15" t="s">
+        <v>893</v>
+      </c>
+      <c r="D164" s="16" t="s">
+        <v>1017</v>
+      </c>
+      <c r="E164" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="165" ht="15.75" customHeight="1">
+      <c r="A165" s="8"/>
+      <c r="B165" s="9" t="s">
+        <v>664</v>
+      </c>
+      <c r="C165" s="9" t="s">
+        <v>509</v>
+      </c>
+      <c r="D165" s="10" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E165" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="166" ht="15.75" customHeight="1">
+      <c r="A166" s="11"/>
+      <c r="B166" s="12" t="s">
+        <v>667</v>
+      </c>
+      <c r="C166" s="12" t="s">
+        <v>976</v>
+      </c>
+      <c r="D166" s="13" t="s">
+        <v>1019</v>
+      </c>
+      <c r="E166" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="167" ht="15.75" customHeight="1">
+      <c r="A167" s="14"/>
+      <c r="B167" s="15" t="s">
+        <v>677</v>
+      </c>
+      <c r="C167" s="15" t="s">
+        <v>678</v>
+      </c>
+      <c r="D167" s="16" t="s">
+        <v>1020</v>
+      </c>
+      <c r="E167" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="168" ht="15.75" customHeight="1">
+      <c r="A168" s="14"/>
+      <c r="B168" s="15" t="s">
+        <v>682</v>
+      </c>
+      <c r="C168" s="15" t="s">
+        <v>698</v>
+      </c>
+      <c r="D168" s="16" t="s">
+        <v>1021</v>
+      </c>
+      <c r="E168" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="169" ht="15.75" customHeight="1">
+      <c r="A169" s="8"/>
+      <c r="B169" s="9" t="s">
+        <v>685</v>
+      </c>
+      <c r="C169" s="9" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D169" s="10" t="s">
+        <v>1023</v>
+      </c>
+      <c r="E169" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="170" ht="15.75" customHeight="1">
+      <c r="A170" s="11"/>
+      <c r="B170" s="12" t="s">
+        <v>688</v>
+      </c>
+      <c r="C170" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="D170" s="13" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E170" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="171" ht="15.75" customHeight="1">
+      <c r="A171" s="8"/>
+      <c r="B171" s="9" t="s">
+        <v>691</v>
+      </c>
+      <c r="C171" s="9" t="s">
+        <v>692</v>
+      </c>
+      <c r="D171" s="10" t="s">
+        <v>1025</v>
+      </c>
+      <c r="E171" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="172" ht="15.75" customHeight="1">
+      <c r="A172" s="8"/>
+      <c r="B172" s="9" t="s">
+        <v>694</v>
+      </c>
+      <c r="C172" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="D172" s="10" t="s">
+        <v>1026</v>
+      </c>
+      <c r="E172" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="173" ht="15.75" customHeight="1">
+      <c r="A173" s="11"/>
+      <c r="B173" s="12" t="s">
+        <v>700</v>
+      </c>
+      <c r="C173" s="12" t="s">
+        <v>1027</v>
+      </c>
+      <c r="D173" s="13" t="s">
+        <v>1028</v>
+      </c>
+      <c r="E173" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="174" ht="15.75" customHeight="1">
+      <c r="A174" s="8"/>
+      <c r="B174" s="9" t="s">
+        <v>706</v>
+      </c>
+      <c r="C174" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="D174" s="10" t="s">
+        <v>1029</v>
+      </c>
+      <c r="E174" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="175" ht="15.75" customHeight="1">
+      <c r="A175" s="11"/>
+      <c r="B175" s="12" t="s">
+        <v>711</v>
+      </c>
+      <c r="C175" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D175" s="13" t="s">
+        <v>1030</v>
+      </c>
+      <c r="E175" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="176" ht="15.75" customHeight="1">
+      <c r="A176" s="14"/>
+      <c r="B176" s="15" t="s">
+        <v>714</v>
+      </c>
+      <c r="C176" s="15" t="s">
+        <v>741</v>
+      </c>
+      <c r="D176" s="16" t="s">
+        <v>1031</v>
+      </c>
+      <c r="E176" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="177" ht="15.75" customHeight="1">
+      <c r="A177" s="11"/>
+      <c r="B177" s="12" t="s">
+        <v>719</v>
+      </c>
+      <c r="C177" s="12" t="s">
+        <v>362</v>
+      </c>
+      <c r="D177" s="13" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E177" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="178" ht="15.75" customHeight="1">
+      <c r="A178" s="14"/>
+      <c r="B178" s="15" t="s">
+        <v>721</v>
+      </c>
+      <c r="C178" s="15" t="s">
+        <v>422</v>
+      </c>
+      <c r="D178" s="16" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E178" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="179" ht="15.75" customHeight="1">
+      <c r="A179" s="8"/>
+      <c r="B179" s="9" t="s">
+        <v>723</v>
+      </c>
+      <c r="C179" s="9" t="s">
+        <v>837</v>
+      </c>
+      <c r="D179" s="10" t="s">
+        <v>1034</v>
+      </c>
+      <c r="E179" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="180" ht="15.75" customHeight="1">
+      <c r="A180" s="11"/>
+      <c r="B180" s="12" t="s">
+        <v>726</v>
+      </c>
+      <c r="C180" s="12" t="s">
+        <v>910</v>
+      </c>
+      <c r="D180" s="13" t="s">
+        <v>1035</v>
+      </c>
+      <c r="E180" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="181" ht="15.75" customHeight="1">
+      <c r="A181" s="14"/>
+      <c r="B181" s="15" t="s">
+        <v>728</v>
+      </c>
+      <c r="C181" s="15" t="s">
+        <v>729</v>
+      </c>
+      <c r="D181" s="16" t="s">
+        <v>1036</v>
+      </c>
+      <c r="E181" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="182" ht="15.75" customHeight="1">
+      <c r="A182" s="8"/>
+      <c r="B182" s="9" t="s">
+        <v>733</v>
+      </c>
+      <c r="C182" s="9" t="s">
+        <v>734</v>
+      </c>
+      <c r="D182" s="10" t="s">
+        <v>1037</v>
+      </c>
+      <c r="E182" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="183" ht="15.75" customHeight="1">
+      <c r="A183" s="11"/>
+      <c r="B183" s="12" t="s">
+        <v>743</v>
+      </c>
+      <c r="C183" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="D183" s="13" t="s">
+        <v>1038</v>
+      </c>
+      <c r="E183" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="184" ht="15.75" customHeight="1">
+      <c r="A184" s="8"/>
+      <c r="B184" s="9" t="s">
+        <v>747</v>
+      </c>
+      <c r="C184" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="D184" s="10" t="s">
+        <v>1039</v>
+      </c>
+      <c r="E184" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="185" ht="15.75" customHeight="1">
+      <c r="A185" s="14"/>
+      <c r="B185" s="15" t="s">
+        <v>747</v>
+      </c>
+      <c r="C185" s="15" t="s">
+        <v>377</v>
+      </c>
+      <c r="D185" s="16" t="s">
+        <v>1040</v>
+      </c>
+      <c r="E185" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="186" ht="15.75" customHeight="1">
+      <c r="A186" s="14"/>
+      <c r="B186" s="15" t="s">
+        <v>751</v>
+      </c>
+      <c r="C186" s="15" t="s">
+        <v>396</v>
+      </c>
+      <c r="D186" s="16" t="s">
+        <v>1041</v>
+      </c>
+      <c r="E186" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="187" ht="15.75" customHeight="1">
+      <c r="A187" s="11"/>
+      <c r="B187" s="12" t="s">
+        <v>757</v>
+      </c>
+      <c r="C187" s="12" t="s">
+        <v>797</v>
+      </c>
+      <c r="D187" s="13" t="s">
+        <v>1042</v>
+      </c>
+      <c r="E187" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="188" ht="15.75" customHeight="1">
+      <c r="A188" s="8"/>
+      <c r="B188" s="9" t="s">
+        <v>761</v>
+      </c>
+      <c r="C188" s="9" t="s">
+        <v>509</v>
+      </c>
+      <c r="D188" s="10" t="s">
+        <v>1043</v>
+      </c>
+      <c r="E188" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="189" ht="15.75" customHeight="1">
+      <c r="A189" s="8"/>
+      <c r="B189" s="9" t="s">
+        <v>764</v>
+      </c>
+      <c r="C189" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="D189" s="10" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E189" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="190" ht="15.75" customHeight="1">
+      <c r="A190" s="11"/>
+      <c r="B190" s="12" t="s">
+        <v>764</v>
+      </c>
+      <c r="C190" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="D190" s="13" t="s">
+        <v>1045</v>
+      </c>
+      <c r="E190" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="191" ht="15.75" customHeight="1">
+      <c r="A191" s="14"/>
+      <c r="B191" s="15" t="s">
+        <v>764</v>
+      </c>
+      <c r="C191" s="15" t="s">
+        <v>698</v>
+      </c>
+      <c r="D191" s="16" t="s">
+        <v>1046</v>
+      </c>
+      <c r="E191" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="192" ht="15.75" customHeight="1">
+      <c r="A192" s="11"/>
+      <c r="B192" s="12" t="s">
+        <v>768</v>
+      </c>
+      <c r="C192" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="D192" s="13" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E192" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="193" ht="15.75" customHeight="1">
+      <c r="A193" s="8"/>
+      <c r="B193" s="9" t="s">
+        <v>768</v>
+      </c>
+      <c r="C193" s="9" t="s">
+        <v>860</v>
+      </c>
+      <c r="D193" s="10" t="s">
+        <v>1048</v>
+      </c>
+      <c r="E193" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="194" ht="15.75" customHeight="1">
+      <c r="A194" s="14"/>
+      <c r="B194" s="15" t="s">
+        <v>774</v>
+      </c>
+      <c r="C194" s="15" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D194" s="16" t="s">
+        <v>1050</v>
+      </c>
+      <c r="E194" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="195" ht="15.75" customHeight="1">
+      <c r="A195" s="11"/>
+      <c r="B195" s="12" t="s">
+        <v>774</v>
+      </c>
+      <c r="C195" s="12" t="s">
+        <v>1051</v>
+      </c>
+      <c r="D195" s="13" t="s">
+        <v>1052</v>
+      </c>
+      <c r="E195" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="196" ht="15.75" customHeight="1">
+      <c r="A196" s="8"/>
+      <c r="B196" s="9" t="s">
+        <v>779</v>
+      </c>
+      <c r="C196" s="9" t="s">
+        <v>780</v>
+      </c>
+      <c r="D196" s="10" t="s">
+        <v>1053</v>
+      </c>
+      <c r="E196" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="197" ht="15.75" customHeight="1">
+      <c r="A197" s="8"/>
+      <c r="B197" s="9" t="s">
+        <v>779</v>
+      </c>
+      <c r="C197" s="9" t="s">
+        <v>837</v>
+      </c>
+      <c r="D197" s="10" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E197" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="198" ht="15.75" customHeight="1">
+      <c r="A198" s="14"/>
+      <c r="B198" s="15" t="s">
+        <v>784</v>
+      </c>
+      <c r="C198" s="15" t="s">
+        <v>422</v>
+      </c>
+      <c r="D198" s="16" t="s">
+        <v>1055</v>
+      </c>
+      <c r="E198" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="199" ht="15.75" customHeight="1">
+      <c r="A199" s="11"/>
+      <c r="B199" s="12" t="s">
+        <v>784</v>
+      </c>
+      <c r="C199" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="D199" s="13" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E199" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="200" ht="15.75" customHeight="1">
+      <c r="A200" s="11"/>
+      <c r="B200" s="12" t="s">
+        <v>789</v>
+      </c>
+      <c r="C200" s="12" t="s">
+        <v>1057</v>
+      </c>
+      <c r="D200" s="13" t="s">
+        <v>1058</v>
+      </c>
+      <c r="E200" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="201" ht="15.75" customHeight="1">
+      <c r="A201" s="11"/>
+      <c r="B201" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C201" s="12" t="s">
+        <v>377</v>
+      </c>
+      <c r="D201" s="13" t="s">
+        <v>1059</v>
+      </c>
+      <c r="E201" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="202" ht="15.75" customHeight="1">
+      <c r="A202" s="11"/>
+      <c r="B202" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C202" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D202" s="13" t="s">
+        <v>1060</v>
+      </c>
+      <c r="E202" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="203" ht="15.75" customHeight="1">
+      <c r="A203" s="11"/>
+      <c r="B203" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="C203" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="D203" s="13" t="s">
+        <v>1061</v>
+      </c>
+      <c r="E203" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="204" ht="15.75" customHeight="1">
+      <c r="A204" s="11"/>
+      <c r="B204" s="12" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C204" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="D204" s="13" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E204" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="205" ht="15.75" customHeight="1">
+      <c r="A205" s="11"/>
+      <c r="B205" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="C205" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="D205" s="13" t="s">
+        <v>1064</v>
+      </c>
+      <c r="E205" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="206" ht="15.75" customHeight="1">
+      <c r="A206" s="11"/>
+      <c r="B206" s="12" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C206" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="D206" s="13" t="s">
+        <v>1066</v>
+      </c>
+      <c r="E206" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="207" ht="15.75" customHeight="1">
+      <c r="A207" s="11"/>
+      <c r="B207" s="12" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C207" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="D207" s="13" t="s">
+        <v>1068</v>
+      </c>
+      <c r="E207" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="208" ht="15.75" customHeight="1">
+      <c r="A208" s="11"/>
+      <c r="B208" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="C208" s="12" t="s">
+        <v>512</v>
+      </c>
+      <c r="D208" s="13" t="s">
+        <v>1069</v>
+      </c>
+      <c r="E208" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="209" ht="15.75" customHeight="1">
+      <c r="A209" s="11"/>
+      <c r="B209" s="12" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C209" s="12" t="s">
+        <v>709</v>
+      </c>
+      <c r="D209" s="13" t="s">
+        <v>1071</v>
+      </c>
+      <c r="E209" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="210" ht="15.75" customHeight="1">
+      <c r="A210" s="11"/>
+      <c r="B210" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="C210" s="12" t="s">
+        <v>551</v>
+      </c>
+      <c r="D210" s="13" t="s">
+        <v>1072</v>
+      </c>
+      <c r="E210" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="211" ht="15.75" customHeight="1">
+      <c r="A211" s="11"/>
+      <c r="B211" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="C211" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="D211" s="13" t="s">
+        <v>1073</v>
+      </c>
+      <c r="E211" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="212" ht="15.75" customHeight="1">
+      <c r="A212" s="11"/>
+      <c r="B212" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="C212" s="12" t="s">
+        <v>365</v>
+      </c>
+      <c r="D212" s="13" t="s">
+        <v>1074</v>
+      </c>
+      <c r="E212" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="213" ht="15.75" customHeight="1">
+      <c r="A213" s="11"/>
+      <c r="B213" s="12" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C213" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="D213" s="13" t="s">
+        <v>1076</v>
+      </c>
+      <c r="E213" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="214" ht="15.75" customHeight="1">
+      <c r="A214" s="11"/>
+      <c r="B214" s="12" t="s">
+        <v>277</v>
+      </c>
+      <c r="C214" s="12" t="s">
+        <v>503</v>
+      </c>
+      <c r="D214" s="13" t="s">
+        <v>1077</v>
+      </c>
+      <c r="E214" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="215" ht="15.75" customHeight="1">
+      <c r="A215" s="11"/>
+      <c r="B215" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="C215" s="12" t="s">
+        <v>817</v>
+      </c>
+      <c r="D215" s="13" t="s">
+        <v>1078</v>
+      </c>
+      <c r="E215" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="216" ht="15.75" customHeight="1">
+      <c r="A216" s="11"/>
+      <c r="B216" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="C216" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="D216" s="13" t="s">
+        <v>1079</v>
+      </c>
+      <c r="E216" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="217" ht="15.75" customHeight="1">
+      <c r="A217" s="11"/>
+      <c r="B217" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="C217" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="D217" s="13" t="s">
+        <v>1080</v>
+      </c>
+      <c r="E217" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="218" ht="15.75" customHeight="1">
+      <c r="A218" s="11"/>
+      <c r="B218" s="12" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C218" s="12" t="s">
+        <v>582</v>
+      </c>
+      <c r="D218" s="13" t="s">
+        <v>1082</v>
+      </c>
+      <c r="E218" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="219" ht="15.75" customHeight="1">
+      <c r="A219" s="11"/>
+      <c r="B219" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="C219" s="12" t="s">
+        <v>1083</v>
+      </c>
+      <c r="D219" s="13" t="s">
+        <v>1084</v>
+      </c>
+      <c r="E219" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="220" ht="15.75" customHeight="1">
+      <c r="A220" s="11"/>
+      <c r="B220" s="12" t="s">
+        <v>379</v>
+      </c>
+      <c r="C220" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="D220" s="13" t="s">
+        <v>1085</v>
+      </c>
+      <c r="E220" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="221" ht="15.75" customHeight="1">
+      <c r="A221" s="11"/>
+      <c r="B221" s="12" t="s">
+        <v>395</v>
+      </c>
+      <c r="C221" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="D221" s="13" t="s">
+        <v>1086</v>
+      </c>
+      <c r="E221" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="222" ht="15.75" customHeight="1">
+      <c r="A222" s="11"/>
+      <c r="B222" s="12" t="s">
+        <v>410</v>
+      </c>
+      <c r="C222" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="D222" s="13" t="s">
+        <v>1087</v>
+      </c>
+      <c r="E222" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="223" ht="15.75" customHeight="1">
+      <c r="A223" s="11"/>
+      <c r="B223" s="12" t="s">
+        <v>427</v>
+      </c>
+      <c r="C223" s="12" t="s">
+        <v>1088</v>
+      </c>
+      <c r="D223" s="13" t="s">
+        <v>1089</v>
+      </c>
+      <c r="E223" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="224" ht="15.75" customHeight="1">
+      <c r="A224" s="11"/>
+      <c r="B224" s="12" t="s">
+        <v>796</v>
+      </c>
+      <c r="C224" s="12" t="s">
+        <v>893</v>
+      </c>
+      <c r="D224" s="13" t="s">
+        <v>1090</v>
+      </c>
+      <c r="E224" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="225" ht="15.75" customHeight="1">
+      <c r="A225" s="11"/>
+      <c r="B225" s="12" t="s">
+        <v>469</v>
+      </c>
+      <c r="C225" s="12" t="s">
+        <v>741</v>
+      </c>
+      <c r="D225" s="13" t="s">
+        <v>1091</v>
+      </c>
+      <c r="E225" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="226" ht="15.75" customHeight="1">
+      <c r="A226" s="11"/>
+      <c r="B226" s="12" t="s">
+        <v>488</v>
+      </c>
+      <c r="C226" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="D226" s="13" t="s">
+        <v>1092</v>
+      </c>
+      <c r="E226" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="227" ht="15.75" customHeight="1">
+      <c r="A227" s="11"/>
+      <c r="B227" s="12" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C227" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D227" s="13" t="s">
+        <v>1094</v>
+      </c>
+      <c r="E227" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="228" ht="15.75" customHeight="1">
+      <c r="A228" s="11"/>
+      <c r="B228" s="12" t="s">
+        <v>520</v>
+      </c>
+      <c r="C228" s="12" t="s">
+        <v>915</v>
+      </c>
+      <c r="D228" s="13" t="s">
+        <v>1095</v>
+      </c>
+      <c r="E228" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="229" ht="15.75" customHeight="1">
+      <c r="A229" s="11"/>
+      <c r="B229" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="C229" s="12" t="s">
+        <v>509</v>
+      </c>
+      <c r="D229" s="13" t="s">
+        <v>1096</v>
+      </c>
+      <c r="E229" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="230" ht="15.75" customHeight="1">
+      <c r="A230" s="11"/>
+      <c r="B230" s="12" t="s">
+        <v>558</v>
+      </c>
+      <c r="C230" s="12" t="s">
+        <v>709</v>
+      </c>
+      <c r="D230" s="13" t="s">
+        <v>1097</v>
+      </c>
+      <c r="E230" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="231" ht="15.75" customHeight="1">
+      <c r="A231" s="11"/>
+      <c r="B231" s="12" t="s">
+        <v>570</v>
+      </c>
+      <c r="C231" s="12" t="s">
+        <v>606</v>
+      </c>
+      <c r="D231" s="13" t="s">
+        <v>1098</v>
+      </c>
+      <c r="E231" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="232" ht="15.75" customHeight="1">
+      <c r="A232" s="11"/>
+      <c r="B232" s="12" t="s">
+        <v>590</v>
+      </c>
+      <c r="C232" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="D232" s="13" t="s">
+        <v>1099</v>
+      </c>
+      <c r="E232" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="233" ht="15.75" customHeight="1">
+      <c r="A233" s="11"/>
+      <c r="B233" s="12" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C233" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="D233" s="13" t="s">
+        <v>1101</v>
+      </c>
+      <c r="E233" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="234" ht="15.75" customHeight="1">
+      <c r="A234" s="11"/>
+      <c r="B234" s="12" t="s">
+        <v>615</v>
+      </c>
+      <c r="C234" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="D234" s="13" t="s">
+        <v>1102</v>
+      </c>
+      <c r="E234" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="235" ht="15.75" customHeight="1">
+      <c r="A235" s="11"/>
+      <c r="B235" s="12" t="s">
+        <v>635</v>
+      </c>
+      <c r="C235" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D235" s="13" t="s">
+        <v>1103</v>
+      </c>
+      <c r="E235" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="236" ht="15.75" customHeight="1">
+      <c r="A236" s="11"/>
+      <c r="B236" s="12" t="s">
+        <v>653</v>
+      </c>
+      <c r="C236" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="D236" s="13" t="s">
+        <v>1104</v>
+      </c>
+      <c r="E236" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="237" ht="15.75" customHeight="1">
+      <c r="A237" s="11"/>
+      <c r="B237" s="12" t="s">
+        <v>671</v>
+      </c>
+      <c r="C237" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="D237" s="13" t="s">
+        <v>1105</v>
+      </c>
+      <c r="E237" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="238" ht="15.75" customHeight="1">
+      <c r="A238" s="11"/>
+      <c r="B238" s="12" t="s">
+        <v>694</v>
+      </c>
+      <c r="C238" s="12" t="s">
+        <v>582</v>
+      </c>
+      <c r="D238" s="13" t="s">
+        <v>1106</v>
+      </c>
+      <c r="E238" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="239" ht="15.75" customHeight="1">
+      <c r="A239" s="11"/>
+      <c r="B239" s="12" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C239" s="12" t="s">
+        <v>1083</v>
+      </c>
+      <c r="D239" s="13" t="s">
+        <v>1108</v>
+      </c>
+      <c r="E239" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="240" ht="15.75" customHeight="1">
+      <c r="A240" s="11"/>
+      <c r="B240" s="12" t="s">
+        <v>733</v>
+      </c>
+      <c r="C240" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="D240" s="13" t="s">
+        <v>1109</v>
+      </c>
+      <c r="E240" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="241" ht="15.75" customHeight="1">
+      <c r="A241" s="11"/>
+      <c r="B241" s="12" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C241" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="D241" s="13" t="s">
+        <v>1111</v>
+      </c>
+      <c r="E241" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="242" ht="15.75" customHeight="1">
+      <c r="A242" s="11"/>
+      <c r="B242" s="12" t="s">
+        <v>774</v>
+      </c>
+      <c r="C242" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="D242" s="13" t="s">
+        <v>1112</v>
+      </c>
+      <c r="E242" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="243" ht="15.75" customHeight="1">
+      <c r="A243" s="8"/>
+      <c r="B243" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C243" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D243" s="10" t="s">
+        <v>1113</v>
+      </c>
+      <c r="E243" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="244" ht="15.75" customHeight="1">
+      <c r="A244" s="8"/>
+      <c r="B244" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C244" s="9" t="s">
+        <v>741</v>
+      </c>
+      <c r="D244" s="10" t="s">
+        <v>1114</v>
+      </c>
+      <c r="E244" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="245" ht="15.75" customHeight="1">
+      <c r="A245" s="8"/>
+      <c r="B245" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C245" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="D245" s="10" t="s">
+        <v>1115</v>
+      </c>
+      <c r="E245" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="246" ht="15.75" customHeight="1">
+      <c r="A246" s="8"/>
+      <c r="B246" s="9" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C246" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D246" s="10" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E246" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="247" ht="15.75" customHeight="1">
+      <c r="A247" s="8"/>
+      <c r="B247" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="C247" s="9" t="s">
+        <v>915</v>
+      </c>
+      <c r="D247" s="10" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E247" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="248" ht="15.75" customHeight="1">
+      <c r="A248" s="8"/>
+      <c r="B248" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C248" s="9" t="s">
+        <v>509</v>
+      </c>
+      <c r="D248" s="10" t="s">
+        <v>1118</v>
+      </c>
+      <c r="E248" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="249" ht="15.75" customHeight="1">
+      <c r="A249" s="8"/>
+      <c r="B249" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="C249" s="9" t="s">
+        <v>709</v>
+      </c>
+      <c r="D249" s="10" t="s">
+        <v>1119</v>
+      </c>
+      <c r="E249" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="250" ht="15.75" customHeight="1">
+      <c r="A250" s="8"/>
+      <c r="B250" s="9" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C250" s="9" t="s">
+        <v>606</v>
+      </c>
+      <c r="D250" s="10" t="s">
+        <v>1121</v>
+      </c>
+      <c r="E250" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="251" ht="15.75" customHeight="1">
+      <c r="A251" s="8"/>
+      <c r="B251" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="C251" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="D251" s="10" t="s">
+        <v>1122</v>
+      </c>
+      <c r="E251" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="252" ht="15.75" customHeight="1">
+      <c r="A252" s="8"/>
+      <c r="B252" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="C252" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="D252" s="10" t="s">
+        <v>1123</v>
+      </c>
+      <c r="E252" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="253" ht="15.75" customHeight="1">
+      <c r="A253" s="8"/>
+      <c r="B253" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="C253" s="9" t="s">
+        <v>486</v>
+      </c>
+      <c r="D253" s="10" t="s">
+        <v>1124</v>
+      </c>
+      <c r="E253" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="254" ht="15.75" customHeight="1">
+      <c r="A254" s="8"/>
+      <c r="B254" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="C254" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="D254" s="10" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E254" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="255" ht="15.75" customHeight="1">
+      <c r="A255" s="8"/>
+      <c r="B255" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="C255" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="D255" s="10" t="s">
+        <v>1126</v>
+      </c>
+      <c r="E255" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="256" ht="15.75" customHeight="1">
+      <c r="A256" s="8"/>
+      <c r="B256" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="C256" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="D256" s="10" t="s">
+        <v>1127</v>
+      </c>
+      <c r="E256" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="257" ht="15.75" customHeight="1">
+      <c r="A257" s="8"/>
+      <c r="B257" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="C257" s="9" t="s">
+        <v>582</v>
+      </c>
+      <c r="D257" s="10" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E257" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="258" ht="15.75" customHeight="1">
+      <c r="A258" s="8"/>
+      <c r="B258" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="C258" s="9" t="s">
+        <v>1083</v>
+      </c>
+      <c r="D258" s="10" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E258" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="259" ht="15.75" customHeight="1">
+      <c r="A259" s="8"/>
+      <c r="B259" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="C259" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D259" s="10" t="s">
+        <v>1130</v>
+      </c>
+      <c r="E259" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="260" ht="15.75" customHeight="1">
+      <c r="A260" s="8"/>
+      <c r="B260" s="9" t="s">
+        <v>920</v>
+      </c>
+      <c r="C260" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="D260" s="10" t="s">
+        <v>1131</v>
+      </c>
+      <c r="E260" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="261" ht="15.75" customHeight="1">
+      <c r="A261" s="8"/>
+      <c r="B261" s="9" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C261" s="9" t="s">
+        <v>380</v>
+      </c>
+      <c r="D261" s="10" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E261" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="262" ht="15.75" customHeight="1">
+      <c r="A262" s="8"/>
+      <c r="B262" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="C262" s="9" t="s">
+        <v>1088</v>
+      </c>
+      <c r="D262" s="10" t="s">
+        <v>1133</v>
+      </c>
+      <c r="E262" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="263" ht="15.75" customHeight="1">
+      <c r="A263" s="8"/>
+      <c r="B263" s="9" t="s">
+        <v>379</v>
+      </c>
+      <c r="C263" s="9" t="s">
+        <v>893</v>
+      </c>
+      <c r="D263" s="10" t="s">
+        <v>1134</v>
+      </c>
+      <c r="E263" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="264" ht="15.75" customHeight="1">
+      <c r="A264" s="8"/>
+      <c r="B264" s="9" t="s">
+        <v>395</v>
+      </c>
+      <c r="C264" s="9" t="s">
+        <v>741</v>
+      </c>
+      <c r="D264" s="10" t="s">
+        <v>1135</v>
+      </c>
+      <c r="E264" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="265" ht="15.75" customHeight="1">
+      <c r="A265" s="8"/>
+      <c r="B265" s="9" t="s">
+        <v>410</v>
+      </c>
+      <c r="C265" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="D265" s="10" t="s">
+        <v>1136</v>
+      </c>
+      <c r="E265" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="266" ht="15.75" customHeight="1">
+      <c r="A266" s="8"/>
+      <c r="B266" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="C266" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D266" s="10" t="s">
+        <v>1137</v>
+      </c>
+      <c r="E266" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="267" ht="15.75" customHeight="1">
+      <c r="A267" s="8"/>
+      <c r="B267" s="9" t="s">
+        <v>448</v>
+      </c>
+      <c r="C267" s="9" t="s">
+        <v>915</v>
+      </c>
+      <c r="D267" s="10" t="s">
+        <v>1138</v>
+      </c>
+      <c r="E267" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="268" ht="15.75" customHeight="1">
+      <c r="A268" s="8"/>
+      <c r="B268" s="9" t="s">
+        <v>467</v>
+      </c>
+      <c r="C268" s="9" t="s">
+        <v>509</v>
+      </c>
+      <c r="D268" s="10" t="s">
+        <v>1139</v>
+      </c>
+      <c r="E268" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="269" ht="15.75" customHeight="1">
+      <c r="A269" s="8"/>
+      <c r="B269" s="9" t="s">
+        <v>485</v>
+      </c>
+      <c r="C269" s="9" t="s">
+        <v>709</v>
+      </c>
+      <c r="D269" s="10" t="s">
+        <v>1140</v>
+      </c>
+      <c r="E269" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="270" ht="15.75" customHeight="1">
+      <c r="A270" s="8"/>
+      <c r="B270" s="9" t="s">
+        <v>502</v>
+      </c>
+      <c r="C270" s="9" t="s">
+        <v>606</v>
+      </c>
+      <c r="D270" s="10" t="s">
+        <v>1141</v>
+      </c>
+      <c r="E270" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="271" ht="15.75" customHeight="1">
+      <c r="A271" s="8"/>
+      <c r="B271" s="9" t="s">
+        <v>518</v>
+      </c>
+      <c r="C271" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="D271" s="10" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E271" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="272" ht="15.75" customHeight="1">
+      <c r="A272" s="8"/>
+      <c r="B272" s="9" t="s">
+        <v>538</v>
+      </c>
+      <c r="C272" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="D272" s="10" t="s">
+        <v>1143</v>
+      </c>
+      <c r="E272" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="273" ht="15.75" customHeight="1">
+      <c r="A273" s="8"/>
+      <c r="B273" s="9" t="s">
+        <v>555</v>
+      </c>
+      <c r="C273" s="9" t="s">
+        <v>486</v>
+      </c>
+      <c r="D273" s="10" t="s">
+        <v>1144</v>
+      </c>
+      <c r="E273" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="274" ht="15.75" customHeight="1">
+      <c r="A274" s="8"/>
+      <c r="B274" s="9" t="s">
+        <v>573</v>
+      </c>
+      <c r="C274" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="D274" s="10" t="s">
+        <v>1145</v>
+      </c>
+      <c r="E274" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="275" ht="15.75" customHeight="1">
+      <c r="A275" s="8"/>
+      <c r="B275" s="9" t="s">
+        <v>593</v>
+      </c>
+      <c r="C275" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="D275" s="10" t="s">
+        <v>1146</v>
+      </c>
+      <c r="E275" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="276" ht="15.75" customHeight="1">
+      <c r="A276" s="8"/>
+      <c r="B276" s="9" t="s">
+        <v>602</v>
+      </c>
+      <c r="C276" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="D276" s="10" t="s">
+        <v>1147</v>
+      </c>
+      <c r="E276" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="277" ht="15.75" customHeight="1">
+      <c r="A277" s="8"/>
+      <c r="B277" s="9" t="s">
+        <v>622</v>
+      </c>
+      <c r="C277" s="9" t="s">
+        <v>582</v>
+      </c>
+      <c r="D277" s="10" t="s">
+        <v>1148</v>
+      </c>
+      <c r="E277" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="278" ht="15.75" customHeight="1">
+      <c r="A278" s="8"/>
+      <c r="B278" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="C278" s="9" t="s">
+        <v>1083</v>
+      </c>
+      <c r="D278" s="10" t="s">
+        <v>1149</v>
+      </c>
+      <c r="E278" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="279" ht="15.75" customHeight="1">
+      <c r="A279" s="8"/>
+      <c r="B279" s="9" t="s">
+        <v>658</v>
+      </c>
+      <c r="C279" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D279" s="10" t="s">
+        <v>1150</v>
+      </c>
+      <c r="E279" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="280" ht="15.75" customHeight="1">
+      <c r="A280" s="8"/>
+      <c r="B280" s="9" t="s">
+        <v>677</v>
+      </c>
+      <c r="C280" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="D280" s="10" t="s">
+        <v>1151</v>
+      </c>
+      <c r="E280" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="281" ht="15.75" customHeight="1">
+      <c r="A281" s="8"/>
+      <c r="B281" s="9" t="s">
+        <v>700</v>
+      </c>
+      <c r="C281" s="9" t="s">
+        <v>380</v>
+      </c>
+      <c r="D281" s="10" t="s">
+        <v>1152</v>
+      </c>
+      <c r="E281" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="282" ht="15.75" customHeight="1">
+      <c r="A282" s="8"/>
+      <c r="B282" s="9" t="s">
+        <v>719</v>
+      </c>
+      <c r="C282" s="9" t="s">
+        <v>1088</v>
+      </c>
+      <c r="D282" s="10" t="s">
+        <v>1153</v>
+      </c>
+      <c r="E282" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="283" ht="15.75" customHeight="1">
+      <c r="A283" s="8"/>
+      <c r="B283" s="9" t="s">
+        <v>738</v>
+      </c>
+      <c r="C283" s="9" t="s">
+        <v>893</v>
+      </c>
+      <c r="D283" s="10" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E283" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="284" ht="15.75" customHeight="1">
+      <c r="A284" s="8"/>
+      <c r="B284" s="9" t="s">
+        <v>755</v>
+      </c>
+      <c r="C284" s="9" t="s">
+        <v>741</v>
+      </c>
+      <c r="D284" s="10" t="s">
+        <v>1155</v>
+      </c>
+      <c r="E284" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="285" ht="15.75" customHeight="1">
+      <c r="A285" s="8"/>
+      <c r="B285" s="9" t="s">
+        <v>784</v>
+      </c>
+      <c r="C285" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="D285" s="10" t="s">
+        <v>1156</v>
+      </c>
+      <c r="E285" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="286" ht="15.75" customHeight="1">
+      <c r="A286" s="14"/>
+      <c r="B286" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C286" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D286" s="16" t="s">
+        <v>1157</v>
+      </c>
+      <c r="E286" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="287" ht="15.75" customHeight="1">
+      <c r="A287" s="14"/>
+      <c r="B287" s="15" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C287" s="15" t="s">
+        <v>915</v>
+      </c>
+      <c r="D287" s="16" t="s">
+        <v>1159</v>
+      </c>
+      <c r="E287" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="288" ht="15.75" customHeight="1">
+      <c r="A288" s="14"/>
+      <c r="B288" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="C288" s="15" t="s">
+        <v>509</v>
+      </c>
+      <c r="D288" s="16" t="s">
+        <v>1160</v>
+      </c>
+      <c r="E288" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="289" ht="15.75" customHeight="1">
+      <c r="A289" s="14"/>
+      <c r="B289" s="15" t="s">
+        <v>230</v>
+      </c>
+      <c r="C289" s="15" t="s">
+        <v>709</v>
+      </c>
+      <c r="D289" s="16" t="s">
+        <v>1161</v>
+      </c>
+      <c r="E289" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="290" ht="15.75" customHeight="1">
+      <c r="A290" s="14"/>
+      <c r="B290" s="15" t="s">
+        <v>325</v>
+      </c>
+      <c r="C290" s="15" t="s">
+        <v>606</v>
+      </c>
+      <c r="D290" s="16" t="s">
+        <v>1162</v>
+      </c>
+      <c r="E290" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="291" ht="15.75" customHeight="1">
+      <c r="A291" s="14"/>
+      <c r="B291" s="15" t="s">
+        <v>390</v>
+      </c>
+      <c r="C291" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="D291" s="16" t="s">
+        <v>1163</v>
+      </c>
+      <c r="E291" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="292" ht="15.75" customHeight="1">
+      <c r="A292" s="14"/>
+      <c r="B292" s="15" t="s">
+        <v>456</v>
+      </c>
+      <c r="C292" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="D292" s="16" t="s">
+        <v>1164</v>
+      </c>
+      <c r="E292" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="293" ht="15.75" customHeight="1">
+      <c r="A293" s="14"/>
+      <c r="B293" s="15" t="s">
+        <v>530</v>
+      </c>
+      <c r="C293" s="15" t="s">
+        <v>486</v>
+      </c>
+      <c r="D293" s="16" t="s">
+        <v>1165</v>
+      </c>
+      <c r="E293" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="294" ht="15.75" customHeight="1">
+      <c r="A294" s="14"/>
+      <c r="B294" s="15" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C294" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="D294" s="16" t="s">
+        <v>1166</v>
+      </c>
+      <c r="E294" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="295" ht="15.75" customHeight="1">
+      <c r="A295" s="14"/>
+      <c r="B295" s="15" t="s">
+        <v>691</v>
+      </c>
+      <c r="C295" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="D295" s="16" t="s">
+        <v>1167</v>
+      </c>
+      <c r="E295" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="296" ht="15.75" customHeight="1">
+      <c r="A296" s="14"/>
+      <c r="B296" s="15" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C296" s="15" t="s">
+        <v>817</v>
+      </c>
+      <c r="D296" s="16" t="s">
+        <v>1169</v>
+      </c>
+      <c r="E296" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="297" ht="15.75" customHeight="1">
+      <c r="A297" s="11"/>
+      <c r="B297" s="12" t="s">
+        <v>625</v>
+      </c>
+      <c r="C297" s="12" t="s">
+        <v>452</v>
+      </c>
+      <c r="D297" s="13" t="s">
+        <v>1170</v>
+      </c>
+      <c r="E297" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="298" ht="15.75" customHeight="1">
+      <c r="A298" s="8"/>
+      <c r="B298" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="C298" s="9" t="s">
+        <v>1171</v>
+      </c>
+      <c r="D298" s="10" t="s">
+        <v>1172</v>
+      </c>
+      <c r="E298" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="299" ht="15.75" customHeight="1">
+      <c r="A299" s="14"/>
+      <c r="B299" s="15" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C299" s="15" t="s">
+        <v>683</v>
+      </c>
+      <c r="D299" s="16" t="s">
+        <v>1174</v>
+      </c>
+      <c r="E299" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="300" ht="15.75" customHeight="1">
+      <c r="A300" s="14"/>
+      <c r="B300" s="15" t="s">
+        <v>728</v>
+      </c>
+      <c r="C300" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="D300" s="16" t="s">
+        <v>1175</v>
+      </c>
+      <c r="E300" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="301" ht="15.75" customHeight="1">
+      <c r="A301" s="8"/>
+      <c r="B301" s="9" t="s">
+        <v>514</v>
+      </c>
+      <c r="C301" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="D301" s="10" t="s">
+        <v>1176</v>
+      </c>
+      <c r="E301" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="302" ht="15.75" customHeight="1">
+      <c r="A302" s="14"/>
+      <c r="B302" s="15" t="s">
+        <v>792</v>
+      </c>
+      <c r="C302" s="15" t="s">
+        <v>817</v>
+      </c>
+      <c r="D302" s="16" t="s">
+        <v>1177</v>
+      </c>
+      <c r="E302" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1"/>
+  </sheetData>
+  <printOptions/>
+  <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
+  <pageSetup orientation="landscape"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -8085,46 +14468,46 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="17" t="s">
-        <v>799</v>
-      </c>
-      <c r="C1" s="17" t="s">
-        <v>800</v>
+      <c r="B1" s="20" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C1" s="20" t="s">
+        <v>1179</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18">
-        <v>1.0</v>
-      </c>
-      <c r="B2" s="19" t="s">
-        <v>801</v>
-      </c>
-      <c r="C2" s="18">
+      <c r="A2" s="21">
+        <v>1.0</v>
+      </c>
+      <c r="B2" s="22" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C2" s="21">
         <v>116.0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="20">
+      <c r="A3" s="23">
         <v>0.0</v>
       </c>
-      <c r="B3" s="21" t="s">
-        <v>802</v>
-      </c>
-      <c r="C3" s="20">
+      <c r="B3" s="24" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C3" s="23">
         <v>67.0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="22">
-        <v>-1.0</v>
-      </c>
-      <c r="B4" s="23" t="s">
-        <v>803</v>
-      </c>
-      <c r="C4" s="22">
+      <c r="A4" s="25">
+        <v>-1.0</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C4" s="25">
         <v>116.0</v>
       </c>
     </row>
